--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BC1CC0-AC4B-468E-B7D8-9BE75353D940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D72EE46-DB7A-4198-80AD-287D29369D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -143,6 +143,10 @@
   </si>
   <si>
     <t>食物开销结余</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午5+晚上8</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -152,7 +156,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="179" formatCode="_ [$¥-804]* #,##0.00_ ;_ [$¥-804]* \-#,##0.00_ ;_ [$¥-804]* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ [$¥-804]* #,##0.00_ ;_ [$¥-804]* \-#,##0.00_ ;_ [$¥-804]* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -214,24 +218,24 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="差" xfId="1" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -269,66 +273,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -711,7 +655,7 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C3:C32)</f>
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3">
@@ -741,6 +685,7 @@
       <c r="B3" s="3">
         <v>13</v>
       </c>
+      <c r="C3" s="4"/>
       <c r="H3" s="7"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -762,6 +707,7 @@
       <c r="B4" s="3">
         <v>13</v>
       </c>
+      <c r="C4" s="4"/>
       <c r="G4" t="s">
         <v>3</v>
       </c>
@@ -783,6 +729,8 @@
       <c r="B5" s="3">
         <v>13</v>
       </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="1"/>
       <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
@@ -792,6 +740,8 @@
       <c r="B6" s="3">
         <v>13</v>
       </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="1"/>
       <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
@@ -801,6 +751,8 @@
       <c r="B7" s="3">
         <v>13</v>
       </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="1"/>
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
@@ -810,6 +762,8 @@
       <c r="B8" s="3">
         <v>13</v>
       </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="1"/>
       <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
@@ -819,6 +773,8 @@
       <c r="B9" s="3">
         <v>13</v>
       </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="1"/>
       <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
@@ -828,6 +784,8 @@
       <c r="B10" s="3">
         <v>13</v>
       </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="1"/>
       <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
@@ -837,6 +795,8 @@
       <c r="B11" s="3">
         <v>13</v>
       </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="1"/>
       <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
@@ -846,6 +806,8 @@
       <c r="B12" s="3">
         <v>13</v>
       </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="1"/>
       <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
@@ -855,6 +817,8 @@
       <c r="B13" s="3">
         <v>13</v>
       </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="1"/>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
@@ -864,6 +828,8 @@
       <c r="B14" s="3">
         <v>13</v>
       </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="1"/>
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
@@ -873,6 +839,8 @@
       <c r="B15" s="3">
         <v>13</v>
       </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="1"/>
       <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
@@ -882,6 +850,8 @@
       <c r="B16" s="3">
         <v>13</v>
       </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="1"/>
       <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -891,6 +861,8 @@
       <c r="B17" s="3">
         <v>13</v>
       </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="1"/>
       <c r="H17" s="7"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -900,6 +872,8 @@
       <c r="B18" s="3">
         <v>13</v>
       </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="1"/>
       <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -909,6 +883,8 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="1"/>
       <c r="H19" s="7"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -918,6 +894,8 @@
       <c r="B20" s="3">
         <v>13</v>
       </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="1"/>
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -927,6 +905,8 @@
       <c r="B21" s="3">
         <v>13</v>
       </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="1"/>
       <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -936,6 +916,8 @@
       <c r="B22" s="3">
         <v>13</v>
       </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="1"/>
       <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -945,6 +927,8 @@
       <c r="B23" s="3">
         <v>13</v>
       </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="1"/>
       <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -983,9 +967,19 @@
       <c r="B25" s="3">
         <v>13</v>
       </c>
+      <c r="C25" s="4">
+        <v>13</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" ref="E25:E30" si="0">B3-C25</f>
+        <v>0</v>
+      </c>
       <c r="H25" s="8">
-        <f t="shared" ref="H25:H36" si="0">SUM(C25,F25)</f>
-        <v>0</v>
+        <f t="shared" ref="H25:H36" si="1">SUM(C25,F25)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -995,8 +989,14 @@
       <c r="B26" s="3">
         <v>13</v>
       </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="3">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
       <c r="H26" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1007,8 +1007,14 @@
       <c r="B27" s="3">
         <v>13</v>
       </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="3">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
       <c r="H27" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1019,8 +1025,14 @@
       <c r="B28" s="3">
         <v>13</v>
       </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="3">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
       <c r="H28" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1031,8 +1043,14 @@
       <c r="B29" s="3">
         <v>13</v>
       </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="3">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
       <c r="H29" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1043,8 +1061,14 @@
       <c r="B30" s="3">
         <v>13</v>
       </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="3">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
       <c r="H30" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1055,13 +1079,13 @@
       <c r="B31" s="3">
         <v>13</v>
       </c>
-      <c r="C31" s="1"/>
+      <c r="C31" s="3"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I31" s="1"/>
@@ -1078,7 +1102,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I32" s="1"/>
@@ -1086,7 +1110,7 @@
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H33" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I33" s="1"/>
@@ -1094,7 +1118,7 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H34" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I34" s="1"/>
@@ -1102,7 +1126,7 @@
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H35" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I35" s="1"/>
@@ -1116,7 +1140,7 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I36" s="1"/>
@@ -1136,16 +1160,16 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="E2:E32">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1160,21 +1184,20 @@
   <cols>
     <col min="1" max="1" width="14.625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.125" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13" customWidth="1"/>
     <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D72EE46-DB7A-4198-80AD-287D29369D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC53418-D679-47AD-BC65-FBACB207B7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="28">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -147,6 +147,10 @@
   </si>
   <si>
     <t>中午5+晚上8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>挤痘痘的工具 12.9</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -643,6 +647,7 @@
       <c r="B2" s="3">
         <v>13</v>
       </c>
+      <c r="F2" s="4"/>
       <c r="H2" s="6"/>
       <c r="I2" s="4"/>
       <c r="J2" s="3">
@@ -655,12 +660,12 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C3:C32)</f>
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3">
         <f>SUM(F3:F32)</f>
-        <v>29.58</v>
+        <v>42.48</v>
       </c>
       <c r="O2" s="3">
         <v>300</v>
@@ -671,7 +676,7 @@
       </c>
       <c r="Q2" s="3">
         <f>SUM(O2:P2)-N2</f>
-        <v>270.42</v>
+        <v>257.52</v>
       </c>
       <c r="R2" s="3"/>
       <c r="S2" s="1"/>
@@ -686,6 +691,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="4"/>
+      <c r="F3" s="4"/>
       <c r="H3" s="7"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -708,6 +714,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="4"/>
+      <c r="F4" s="4"/>
       <c r="G4" t="s">
         <v>3</v>
       </c>
@@ -731,6 +738,7 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="1"/>
+      <c r="F5" s="4"/>
       <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
@@ -742,6 +750,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="1"/>
+      <c r="F6" s="4"/>
       <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
@@ -753,6 +762,7 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
+      <c r="F7" s="4"/>
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
@@ -764,6 +774,7 @@
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
+      <c r="F8" s="4"/>
       <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
@@ -775,6 +786,7 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="1"/>
+      <c r="F9" s="4"/>
       <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
@@ -786,6 +798,7 @@
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="1"/>
+      <c r="F10" s="4"/>
       <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
@@ -797,6 +810,7 @@
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="1"/>
+      <c r="F11" s="4"/>
       <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
@@ -808,6 +822,7 @@
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="1"/>
+      <c r="F12" s="4"/>
       <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
@@ -819,6 +834,7 @@
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="1"/>
+      <c r="F13" s="4"/>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
@@ -830,6 +846,7 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="1"/>
+      <c r="F14" s="4"/>
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
@@ -841,6 +858,7 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="1"/>
+      <c r="F15" s="4"/>
       <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
@@ -852,6 +870,7 @@
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="1"/>
+      <c r="F16" s="4"/>
       <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -863,6 +882,7 @@
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="1"/>
+      <c r="F17" s="4"/>
       <c r="H17" s="7"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -874,6 +894,7 @@
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="1"/>
+      <c r="F18" s="4"/>
       <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -885,6 +906,7 @@
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="1"/>
+      <c r="F19" s="4"/>
       <c r="H19" s="7"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -896,6 +918,7 @@
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="1"/>
+      <c r="F20" s="4"/>
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -907,6 +930,7 @@
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="1"/>
+      <c r="F21" s="4"/>
       <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -918,6 +942,7 @@
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="1"/>
+      <c r="F22" s="4"/>
       <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -929,6 +954,7 @@
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="1"/>
+      <c r="F23" s="4"/>
       <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -977,6 +1003,7 @@
         <f t="shared" ref="E25:E30" si="0">B3-C25</f>
         <v>0</v>
       </c>
+      <c r="F25" s="4"/>
       <c r="H25" s="8">
         <f t="shared" ref="H25:H36" si="1">SUM(C25,F25)</f>
         <v>13</v>
@@ -989,15 +1016,25 @@
       <c r="B26" s="3">
         <v>13</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="C26" s="3">
+        <v>10</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>3</v>
+      </c>
+      <c r="F26" s="4">
+        <v>12.9</v>
+      </c>
+      <c r="G26" t="s">
+        <v>27</v>
       </c>
       <c r="H26" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -1013,6 +1050,7 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
+      <c r="F27" s="4"/>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1031,6 +1069,7 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
+      <c r="F28" s="4"/>
       <c r="H28" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1049,6 +1088,7 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
+      <c r="F29" s="4"/>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1067,6 +1107,7 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
+      <c r="F30" s="4"/>
       <c r="H30" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1082,7 +1123,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
+      <c r="F31" s="3"/>
       <c r="G31" s="1"/>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
@@ -1099,7 +1140,7 @@
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
+      <c r="F32" s="3"/>
       <c r="G32" s="1"/>
       <c r="H32" s="8">
         <f t="shared" si="1"/>
@@ -1109,6 +1150,7 @@
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="F33" s="4"/>
       <c r="H33" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1117,6 +1159,7 @@
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="F34" s="4"/>
       <c r="H34" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1125,6 +1168,7 @@
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="F35" s="4"/>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
         <v>0</v>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC53418-D679-47AD-BC65-FBACB207B7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04B2630-F120-4387-913B-9C585BD8771F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1065" yWindow="4650" windowWidth="17445" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="29">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -152,6 +152,9 @@
   <si>
     <t>挤痘痘的工具 12.9</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午5+晚上6</t>
   </si>
 </sst>
 </file>
@@ -556,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.625" bestFit="1" customWidth="1"/>
@@ -648,6 +651,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="4"/>
+      <c r="G2" s="1"/>
       <c r="H2" s="6"/>
       <c r="I2" s="4"/>
       <c r="J2" s="3">
@@ -660,7 +664,7 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C3:C32)</f>
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3">
@@ -668,7 +672,8 @@
         <v>42.48</v>
       </c>
       <c r="O2" s="3">
-        <v>300</v>
+        <f>300-200+100</f>
+        <v>200</v>
       </c>
       <c r="P2" s="3">
         <f>SUM(J5:J48)</f>
@@ -676,7 +681,7 @@
       </c>
       <c r="Q2" s="3">
         <f>SUM(O2:P2)-N2</f>
-        <v>257.52</v>
+        <v>157.52000000000001</v>
       </c>
       <c r="R2" s="3"/>
       <c r="S2" s="1"/>
@@ -692,6 +697,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="F3" s="4"/>
+      <c r="G3" s="1"/>
       <c r="H3" s="7"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -715,7 +721,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H4" s="7"/>
@@ -739,6 +745,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="1"/>
       <c r="F5" s="4"/>
+      <c r="G5" s="1"/>
       <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
@@ -751,6 +758,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="1"/>
       <c r="F6" s="4"/>
+      <c r="G6" s="1"/>
       <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
@@ -763,6 +771,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="F7" s="4"/>
+      <c r="G7" s="1"/>
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
@@ -775,6 +784,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="F8" s="4"/>
+      <c r="G8" s="1"/>
       <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
@@ -787,6 +797,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="1"/>
       <c r="F9" s="4"/>
+      <c r="G9" s="1"/>
       <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
@@ -799,6 +810,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="1"/>
       <c r="F10" s="4"/>
+      <c r="G10" s="1"/>
       <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
@@ -811,6 +823,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="1"/>
       <c r="F11" s="4"/>
+      <c r="G11" s="1"/>
       <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
@@ -823,6 +836,7 @@
       <c r="C12" s="4"/>
       <c r="D12" s="1"/>
       <c r="F12" s="4"/>
+      <c r="G12" s="1"/>
       <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
@@ -835,6 +849,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="1"/>
       <c r="F13" s="4"/>
+      <c r="G13" s="1"/>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
@@ -847,6 +862,7 @@
       <c r="C14" s="4"/>
       <c r="D14" s="1"/>
       <c r="F14" s="4"/>
+      <c r="G14" s="1"/>
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
@@ -859,6 +875,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="1"/>
       <c r="F15" s="4"/>
+      <c r="G15" s="1"/>
       <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
@@ -871,6 +888,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="1"/>
       <c r="F16" s="4"/>
+      <c r="G16" s="1"/>
       <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -883,6 +901,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="1"/>
       <c r="F17" s="4"/>
+      <c r="G17" s="1"/>
       <c r="H17" s="7"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -895,6 +914,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="1"/>
       <c r="F18" s="4"/>
+      <c r="G18" s="1"/>
       <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -907,6 +927,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="1"/>
       <c r="F19" s="4"/>
+      <c r="G19" s="1"/>
       <c r="H19" s="7"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -919,6 +940,7 @@
       <c r="C20" s="4"/>
       <c r="D20" s="1"/>
       <c r="F20" s="4"/>
+      <c r="G20" s="1"/>
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -931,6 +953,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="1"/>
       <c r="F21" s="4"/>
+      <c r="G21" s="1"/>
       <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -943,6 +966,7 @@
       <c r="C22" s="4"/>
       <c r="D22" s="1"/>
       <c r="F22" s="4"/>
+      <c r="G22" s="1"/>
       <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -955,6 +979,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="1"/>
       <c r="F23" s="4"/>
+      <c r="G23" s="1"/>
       <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -1004,6 +1029,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="4"/>
+      <c r="G25" s="1"/>
       <c r="H25" s="8">
         <f t="shared" ref="H25:H36" si="1">SUM(C25,F25)</f>
         <v>13</v>
@@ -1029,7 +1055,7 @@
       <c r="F26" s="4">
         <v>12.9</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H26" s="8">
@@ -1044,16 +1070,21 @@
       <c r="B27" s="3">
         <v>13</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="C27" s="3">
+        <v>10</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F27" s="4"/>
+      <c r="G27" s="1"/>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -1070,6 +1101,7 @@
         <v>13</v>
       </c>
       <c r="F28" s="4"/>
+      <c r="G28" s="1"/>
       <c r="H28" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1089,6 +1121,7 @@
         <v>13</v>
       </c>
       <c r="F29" s="4"/>
+      <c r="G29" s="1"/>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1108,6 +1141,7 @@
         <v>13</v>
       </c>
       <c r="F30" s="4"/>
+      <c r="G30" s="1"/>
       <c r="H30" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1151,6 +1185,7 @@
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.2">
       <c r="F33" s="4"/>
+      <c r="G33" s="1"/>
       <c r="H33" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1160,6 +1195,7 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
       <c r="F34" s="4"/>
+      <c r="G34" s="1"/>
       <c r="H34" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1169,6 +1205,7 @@
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.2">
       <c r="F35" s="4"/>
+      <c r="G35" s="1"/>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1200,6 +1237,15 @@
       <c r="H37" s="5"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="G40" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04B2630-F120-4387-913B-9C585BD8771F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DD80AC-C6F9-4BED-9620-4553EC15B93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1065" yWindow="4650" windowWidth="17445" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8250" yWindow="4230" windowWidth="23775" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="32">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -154,7 +154,20 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>中午5+晚上6</t>
+    <t>中午5+晚上4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚饭 8.8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>往返学校的车票钱 10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>压缩饼干 16.69</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -664,12 +677,12 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C3:C32)</f>
-        <v>43</v>
+        <v>68.8</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3">
         <f>SUM(F3:F32)</f>
-        <v>42.48</v>
+        <v>69.17</v>
       </c>
       <c r="O2" s="3">
         <f>300-200+100</f>
@@ -681,7 +694,7 @@
       </c>
       <c r="Q2" s="3">
         <f>SUM(O2:P2)-N2</f>
-        <v>157.52000000000001</v>
+        <v>130.82999999999998</v>
       </c>
       <c r="R2" s="3"/>
       <c r="S2" s="1"/>
@@ -1074,7 +1087,7 @@
         <v>10</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
@@ -1094,17 +1107,21 @@
       <c r="B28" s="3">
         <v>13</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="C28" s="3">
+        <v>9</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="1"/>
       <c r="H28" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -1114,17 +1131,25 @@
       <c r="B29" s="3">
         <v>13</v>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="C29" s="4">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="1"/>
+        <v>4.1999999999999993</v>
+      </c>
+      <c r="F29" s="4">
+        <v>10</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
@@ -1134,17 +1159,25 @@
       <c r="B30" s="3">
         <v>13</v>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="C30" s="4">
+        <v>8</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="F30" s="4">
+        <v>16.690000000000001</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="H30" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24.69</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DD80AC-C6F9-4BED-9620-4553EC15B93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5DCD3D-EA25-42B9-A5CD-C020825B56CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8250" yWindow="4230" windowWidth="23775" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="8250" yWindow="4230" windowWidth="23775" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="34">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -167,6 +167,13 @@
   </si>
   <si>
     <t>压缩饼干 16.69</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午5+晚上6</t>
+  </si>
+  <si>
+    <t>结余</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -581,7 +588,7 @@
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.25" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
@@ -672,12 +679,12 @@
         <v>13</v>
       </c>
       <c r="K2" s="3">
-        <f>15*COUNT(A2:A31)-22*13</f>
-        <v>164</v>
+        <f>15*COUNT(A2:A33)-22*13</f>
+        <v>179</v>
       </c>
       <c r="L2" s="3">
         <f>SUM(C3:C32)</f>
-        <v>68.8</v>
+        <v>88.8</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3">
@@ -1038,7 +1045,7 @@
         <v>26</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" ref="E25:E30" si="0">B3-C25</f>
+        <f t="shared" ref="E25:E32" si="0">B3-C25</f>
         <v>0</v>
       </c>
       <c r="F25" s="4"/>
@@ -1187,14 +1194,21 @@
       <c r="B31" s="3">
         <v>13</v>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
+      <c r="C31" s="3">
+        <v>10</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
       <c r="F31" s="3"/>
       <c r="G31" s="1"/>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -1203,15 +1217,24 @@
       <c r="A32" s="2">
         <v>46112</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+      <c r="B32" s="3">
+        <v>13</v>
+      </c>
+      <c r="C32" s="3">
+        <v>10</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
       <c r="F32" s="3"/>
       <c r="G32" s="1"/>
       <c r="H32" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -1272,7 +1295,18 @@
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="D38" t="s">
+        <v>33</v>
+      </c>
+      <c r="E38">
+        <f>SUM(E2:E32)</f>
+        <v>28.2</v>
+      </c>
       <c r="G38" s="1"/>
+      <c r="H38" s="4">
+        <f>SUM(H2:H32)</f>
+        <v>157.97</v>
+      </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G39" s="1"/>
@@ -1388,29 +1422,33 @@
         <v>46113</v>
       </c>
       <c r="B2" s="3">
-        <v>13</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="C2" s="3">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="1"/>
       <c r="H2" s="6">
         <f>SUM(C2,F2)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="3">
         <f>AVERAGE(B2:B32)</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K2" s="3">
-        <f>15*COUNT(A2:A31)</f>
-        <v>450</v>
+        <f>SUM(B2:B31)</f>
+        <v>330</v>
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
@@ -1437,7 +1475,7 @@
         <v>46114</v>
       </c>
       <c r="B3" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1456,7 +1494,7 @@
         <v>46115</v>
       </c>
       <c r="B4" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
         <v>3</v>
@@ -1476,7 +1514,7 @@
         <v>46116</v>
       </c>
       <c r="B5" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.2">
@@ -1484,7 +1522,7 @@
         <v>46117</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
@@ -1492,7 +1530,7 @@
         <v>46118</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
@@ -1500,7 +1538,7 @@
         <v>46119</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.2">
@@ -1508,7 +1546,7 @@
         <v>46120</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.2">
@@ -1516,7 +1554,7 @@
         <v>46121</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
@@ -1524,7 +1562,7 @@
         <v>46122</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
@@ -1532,7 +1570,7 @@
         <v>46123</v>
       </c>
       <c r="B12" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
@@ -1540,7 +1578,7 @@
         <v>46124</v>
       </c>
       <c r="B13" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
@@ -1548,7 +1586,7 @@
         <v>46125</v>
       </c>
       <c r="B14" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
@@ -1556,7 +1594,7 @@
         <v>46126</v>
       </c>
       <c r="B15" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
@@ -1564,7 +1602,7 @@
         <v>46127</v>
       </c>
       <c r="B16" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -1572,7 +1610,7 @@
         <v>46128</v>
       </c>
       <c r="B17" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -1580,7 +1618,7 @@
         <v>46129</v>
       </c>
       <c r="B18" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -1588,7 +1626,7 @@
         <v>46130</v>
       </c>
       <c r="B19" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -1596,7 +1634,7 @@
         <v>46131</v>
       </c>
       <c r="B20" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -1604,7 +1642,7 @@
         <v>46132</v>
       </c>
       <c r="B21" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -1612,7 +1650,7 @@
         <v>46133</v>
       </c>
       <c r="B22" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -1620,7 +1658,7 @@
         <v>46134</v>
       </c>
       <c r="B23" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -1628,7 +1666,7 @@
         <v>46135</v>
       </c>
       <c r="B24" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -1636,7 +1674,7 @@
         <v>46136</v>
       </c>
       <c r="B25" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -1644,7 +1682,7 @@
         <v>46137</v>
       </c>
       <c r="B26" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -1652,7 +1690,7 @@
         <v>46138</v>
       </c>
       <c r="B27" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -1660,7 +1698,7 @@
         <v>46139</v>
       </c>
       <c r="B28" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -1668,7 +1706,7 @@
         <v>46140</v>
       </c>
       <c r="B29" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
@@ -1676,7 +1714,7 @@
         <v>46141</v>
       </c>
       <c r="B30" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
@@ -1684,7 +1722,7 @@
         <v>46142</v>
       </c>
       <c r="B31" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -1812,8 +1850,5 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="K2" formulaRange="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5DCD3D-EA25-42B9-A5CD-C020825B56CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160E49F9-3A1B-4D99-A0FB-375B242C893D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="8250" yWindow="4230" windowWidth="23775" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8250" yWindow="4230" windowWidth="23775" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="33">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -168,9 +168,6 @@
   <si>
     <t>压缩饼干 16.69</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中午5+晚上6</t>
   </si>
   <si>
     <t>结余</t>
@@ -1296,7 +1293,7 @@
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.2">
       <c r="D38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E38">
         <f>SUM(E2:E32)</f>
@@ -1428,7 +1425,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -1448,7 +1445,7 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
@@ -1476,6 +1473,16 @@
       </c>
       <c r="B3" s="3">
         <v>11</v>
+      </c>
+      <c r="C3" s="3">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="6">
+        <f t="shared" ref="H3:H34" si="0">SUM(C3,F3)</f>
+        <v>10</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -1499,6 +1506,10 @@
       <c r="G4" t="s">
         <v>3</v>
       </c>
+      <c r="H4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="J4" t="s">
         <v>23</v>
       </c>
@@ -1516,6 +1527,10 @@
       <c r="B5" s="3">
         <v>11</v>
       </c>
+      <c r="H5" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
@@ -1524,6 +1539,10 @@
       <c r="B6" s="3">
         <v>11</v>
       </c>
+      <c r="H6" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
@@ -1532,6 +1551,10 @@
       <c r="B7" s="3">
         <v>11</v>
       </c>
+      <c r="H7" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
@@ -1540,6 +1563,10 @@
       <c r="B8" s="3">
         <v>11</v>
       </c>
+      <c r="H8" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
@@ -1548,6 +1575,10 @@
       <c r="B9" s="3">
         <v>11</v>
       </c>
+      <c r="H9" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
@@ -1556,6 +1587,10 @@
       <c r="B10" s="3">
         <v>11</v>
       </c>
+      <c r="H10" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
@@ -1564,6 +1599,10 @@
       <c r="B11" s="3">
         <v>11</v>
       </c>
+      <c r="H11" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
@@ -1572,6 +1611,10 @@
       <c r="B12" s="3">
         <v>11</v>
       </c>
+      <c r="H12" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
@@ -1580,6 +1623,10 @@
       <c r="B13" s="3">
         <v>11</v>
       </c>
+      <c r="H13" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
@@ -1588,6 +1635,10 @@
       <c r="B14" s="3">
         <v>11</v>
       </c>
+      <c r="H14" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
@@ -1596,6 +1647,10 @@
       <c r="B15" s="3">
         <v>11</v>
       </c>
+      <c r="H15" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
@@ -1604,6 +1659,10 @@
       <c r="B16" s="3">
         <v>11</v>
       </c>
+      <c r="H16" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
@@ -1612,6 +1671,10 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
+      <c r="H17" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
@@ -1620,6 +1683,10 @@
       <c r="B18" s="3">
         <v>11</v>
       </c>
+      <c r="H18" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
@@ -1628,6 +1695,10 @@
       <c r="B19" s="3">
         <v>11</v>
       </c>
+      <c r="H19" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
@@ -1636,6 +1707,10 @@
       <c r="B20" s="3">
         <v>11</v>
       </c>
+      <c r="H20" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
@@ -1644,6 +1719,10 @@
       <c r="B21" s="3">
         <v>11</v>
       </c>
+      <c r="H21" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
@@ -1652,6 +1731,10 @@
       <c r="B22" s="3">
         <v>11</v>
       </c>
+      <c r="H22" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
@@ -1660,6 +1743,10 @@
       <c r="B23" s="3">
         <v>11</v>
       </c>
+      <c r="H23" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
@@ -1668,6 +1755,10 @@
       <c r="B24" s="3">
         <v>11</v>
       </c>
+      <c r="H24" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
@@ -1676,6 +1767,10 @@
       <c r="B25" s="3">
         <v>11</v>
       </c>
+      <c r="H25" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
@@ -1684,6 +1779,10 @@
       <c r="B26" s="3">
         <v>11</v>
       </c>
+      <c r="H26" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
@@ -1692,6 +1791,10 @@
       <c r="B27" s="3">
         <v>11</v>
       </c>
+      <c r="H27" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
@@ -1700,6 +1803,10 @@
       <c r="B28" s="3">
         <v>11</v>
       </c>
+      <c r="H28" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
@@ -1708,6 +1815,10 @@
       <c r="B29" s="3">
         <v>11</v>
       </c>
+      <c r="H29" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
@@ -1715,6 +1826,10 @@
       </c>
       <c r="B30" s="3">
         <v>11</v>
+      </c>
+      <c r="H30" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
@@ -1729,7 +1844,10 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="5"/>
+      <c r="H31" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
@@ -1743,15 +1861,26 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="5"/>
+      <c r="H32" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H33" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H34" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160E49F9-3A1B-4D99-A0FB-375B242C893D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3FFFC3A-08C2-4090-A024-59B8E7AC479C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8250" yWindow="4230" windowWidth="23775" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2955" yWindow="1785" windowWidth="34110" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="39">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -171,6 +171,30 @@
   </si>
   <si>
     <t>结余</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午办公室 包餐+ 晚上 压缩饼干</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>克称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>维生素c 30g 4.3 + 维生素b祖片 7.49 + 咸鱼鸭腿 720g 11.9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午 压缩饼干+ 晚上 8.8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午 压缩饼干 + 晚上 压缩饼干</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是/否</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -178,11 +202,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="44" formatCode="_ &quot;¥&quot;* #,##0.00_ ;_ &quot;¥&quot;* \-#,##0.00_ ;_ &quot;¥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="177" formatCode="_ [$¥-804]* #,##0.00_ ;_ [$¥-804]* \-#,##0.00_ ;_ [$¥-804]* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,6 +228,13 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -228,13 +260,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -254,10 +289,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="差" xfId="1" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -1338,9 +1377,10 @@
   <cols>
     <col min="1" max="1" width="14.625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="53.625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.125" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
@@ -1445,11 +1485,11 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>20</v>
+        <v>28.8</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
-        <v>0</v>
+        <v>37.49</v>
       </c>
       <c r="N2" s="3">
         <v>300</v>
@@ -1460,7 +1500,7 @@
       </c>
       <c r="P2" s="3">
         <f>SUM(N2:O2)-M2</f>
-        <v>300</v>
+        <v>262.51</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="1"/>
@@ -1480,6 +1520,9 @@
       <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
       <c r="H3" s="6">
         <f t="shared" ref="H3:H34" si="0">SUM(C3,F3)</f>
         <v>10</v>
@@ -1503,7 +1546,15 @@
       <c r="B4" s="3">
         <v>11</v>
       </c>
-      <c r="G4" t="s">
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H4" s="6">
@@ -1518,6 +1569,9 @@
       </c>
       <c r="L4" t="s">
         <v>24</v>
+      </c>
+      <c r="M4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.2">
@@ -1527,9 +1581,22 @@
       <c r="B5" s="3">
         <v>11</v>
       </c>
+      <c r="C5" s="3">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="9">
+        <v>13.9</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="H5" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22.700000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.2">
@@ -1539,9 +1606,23 @@
       <c r="B6" s="3">
         <v>11</v>
       </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="9">
+        <f>7.39+4.3+11.9</f>
+        <v>23.59</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="H6" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23.59</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
@@ -1551,6 +1632,13 @@
       <c r="B7" s="3">
         <v>11</v>
       </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
       <c r="H7" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1563,6 +1651,13 @@
       <c r="B8" s="3">
         <v>11</v>
       </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
       <c r="H8" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1575,6 +1670,11 @@
       <c r="B9" s="3">
         <v>11</v>
       </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
       <c r="H9" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1587,6 +1687,11 @@
       <c r="B10" s="3">
         <v>11</v>
       </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
       <c r="H10" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1599,6 +1704,11 @@
       <c r="B11" s="3">
         <v>11</v>
       </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
       <c r="H11" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1611,6 +1721,11 @@
       <c r="B12" s="3">
         <v>11</v>
       </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
       <c r="H12" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1623,6 +1738,11 @@
       <c r="B13" s="3">
         <v>11</v>
       </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
       <c r="H13" s="6">
         <f t="shared" si="0"/>
         <v>0</v>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3FFFC3A-08C2-4090-A024-59B8E7AC479C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A742103D-3F68-4BD5-885E-8138D489CB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2955" yWindow="1785" windowWidth="34110" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4110" yWindow="4815" windowWidth="34110" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="40">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -195,6 +195,10 @@
   </si>
   <si>
     <t>是/否</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>焖子 450g 3.81 + 牛蹄 500g 7.6</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1489,7 +1493,7 @@
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
-        <v>37.49</v>
+        <v>48.900000000000006</v>
       </c>
       <c r="N2" s="3">
         <v>300</v>
@@ -1500,7 +1504,7 @@
       </c>
       <c r="P2" s="3">
         <f>SUM(N2:O2)-M2</f>
-        <v>262.51</v>
+        <v>251.1</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="1"/>
@@ -1637,11 +1641,16 @@
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="F7" s="9">
+        <f>3.81+7.6</f>
+        <v>11.41</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="H7" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A742103D-3F68-4BD5-885E-8138D489CB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CC5765-6D19-4E14-BF4F-AD518F040F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4110" yWindow="4815" windowWidth="34110" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="40">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -273,7 +273,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -296,6 +296,7 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="差" xfId="1" builtinId="27"/>
@@ -1489,7 +1490,7 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>28.8</v>
+        <v>68.8</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
@@ -1637,9 +1638,11 @@
         <v>11</v>
       </c>
       <c r="C7" s="3">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E7" s="1"/>
       <c r="F7" s="9">
         <f>3.81+7.6</f>
@@ -1650,7 +1653,7 @@
       </c>
       <c r="H7" s="6">
         <f t="shared" si="0"/>
-        <v>11.41</v>
+        <v>21.41</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
@@ -1661,15 +1664,17 @@
         <v>11</v>
       </c>
       <c r="C8" s="3">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.2">
@@ -1679,14 +1684,18 @@
       <c r="B9" s="3">
         <v>11</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="C9" s="9">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.2">
@@ -1696,14 +1705,18 @@
       <c r="B10" s="3">
         <v>11</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="C10" s="9">
+        <v>10</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
@@ -1713,7 +1726,7 @@
       <c r="B11" s="3">
         <v>11</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="9"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -1730,7 +1743,7 @@
       <c r="B12" s="3">
         <v>11</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="9"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -1747,7 +1760,7 @@
       <c r="B13" s="3">
         <v>11</v>
       </c>
-      <c r="C13" s="1"/>
+      <c r="C13" s="9"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -1764,6 +1777,7 @@
       <c r="B14" s="3">
         <v>11</v>
       </c>
+      <c r="C14" s="10"/>
       <c r="H14" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1776,6 +1790,7 @@
       <c r="B15" s="3">
         <v>11</v>
       </c>
+      <c r="C15" s="10"/>
       <c r="H15" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1788,6 +1803,7 @@
       <c r="B16" s="3">
         <v>11</v>
       </c>
+      <c r="C16" s="10"/>
       <c r="H16" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1800,6 +1816,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
+      <c r="C17" s="10"/>
       <c r="H17" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1812,6 +1829,7 @@
       <c r="B18" s="3">
         <v>11</v>
       </c>
+      <c r="C18" s="10"/>
       <c r="H18" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1824,6 +1842,7 @@
       <c r="B19" s="3">
         <v>11</v>
       </c>
+      <c r="C19" s="10"/>
       <c r="H19" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1836,6 +1855,7 @@
       <c r="B20" s="3">
         <v>11</v>
       </c>
+      <c r="C20" s="10"/>
       <c r="H20" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1848,6 +1868,7 @@
       <c r="B21" s="3">
         <v>11</v>
       </c>
+      <c r="C21" s="10"/>
       <c r="H21" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1860,6 +1881,7 @@
       <c r="B22" s="3">
         <v>11</v>
       </c>
+      <c r="C22" s="10"/>
       <c r="H22" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1872,6 +1894,7 @@
       <c r="B23" s="3">
         <v>11</v>
       </c>
+      <c r="C23" s="10"/>
       <c r="H23" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1884,6 +1907,7 @@
       <c r="B24" s="3">
         <v>11</v>
       </c>
+      <c r="C24" s="10"/>
       <c r="H24" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1896,6 +1920,7 @@
       <c r="B25" s="3">
         <v>11</v>
       </c>
+      <c r="C25" s="10"/>
       <c r="H25" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1908,6 +1933,7 @@
       <c r="B26" s="3">
         <v>11</v>
       </c>
+      <c r="C26" s="10"/>
       <c r="H26" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1920,6 +1946,7 @@
       <c r="B27" s="3">
         <v>11</v>
       </c>
+      <c r="C27" s="10"/>
       <c r="H27" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1932,6 +1959,7 @@
       <c r="B28" s="3">
         <v>11</v>
       </c>
+      <c r="C28" s="10"/>
       <c r="H28" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1944,6 +1972,7 @@
       <c r="B29" s="3">
         <v>11</v>
       </c>
+      <c r="C29" s="10"/>
       <c r="H29" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1956,6 +1985,7 @@
       <c r="B30" s="3">
         <v>11</v>
       </c>
+      <c r="C30" s="10"/>
       <c r="H30" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1968,7 +1998,7 @@
       <c r="B31" s="3">
         <v>11</v>
       </c>
-      <c r="C31" s="1"/>
+      <c r="C31" s="9"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CC5765-6D19-4E14-BF4F-AD518F040F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA9544E-9EC5-4DBB-A92C-B0BFA15FA297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="4815" windowWidth="34110" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1485" yWindow="4755" windowWidth="34110" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="44">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -199,6 +199,22 @@
   </si>
   <si>
     <t>焖子 450g 3.81 + 牛蹄 500g 7.6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午5+晚上 压缩饼干</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>驴焖子是垃圾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛蹄是非常油腻</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>压缩饼干吃起来还行，吃完了</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1389,7 +1405,7 @@
     <col min="8" max="8" width="7.125" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.625" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="11" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
@@ -1490,7 +1506,7 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>68.8</v>
+        <v>93.8</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
@@ -1501,11 +1517,11 @@
       </c>
       <c r="O2" s="3">
         <f>SUM(J5:J48)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P2" s="3">
-        <f>SUM(N2:O2)-M2</f>
-        <v>251.1</v>
+        <f>SUM(N2:O2)-M2+SUM(J5:J35)</f>
+        <v>271.10000000000002</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="1"/>
@@ -1566,10 +1582,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L4" t="s">
@@ -1602,6 +1618,12 @@
       <c r="H5" s="6">
         <f t="shared" si="0"/>
         <v>22.700000000000003</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.2">
@@ -1629,6 +1651,12 @@
         <f t="shared" si="0"/>
         <v>23.59</v>
       </c>
+      <c r="J6" s="9">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
@@ -1655,6 +1683,12 @@
         <f t="shared" si="0"/>
         <v>21.41</v>
       </c>
+      <c r="J7" s="9">
+        <v>10</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
@@ -1676,6 +1710,8 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="J8" s="9"/>
+      <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
@@ -1697,6 +1733,8 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
@@ -1718,6 +1756,8 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="J10" s="9"/>
+      <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
@@ -1726,15 +1766,21 @@
       <c r="B11" s="3">
         <v>11</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="1"/>
+      <c r="C11" s="9">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J11" s="9"/>
+      <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
@@ -1743,15 +1789,21 @@
       <c r="B12" s="3">
         <v>11</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="1"/>
+      <c r="C12" s="9">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J12" s="9"/>
+      <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
@@ -1760,15 +1812,21 @@
       <c r="B13" s="3">
         <v>11</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="1"/>
+      <c r="C13" s="9">
+        <v>10</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J13" s="9"/>
+      <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
@@ -1782,6 +1840,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="J14" s="10"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
@@ -1795,6 +1854,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
@@ -1808,6 +1868,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
@@ -1821,6 +1882,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
@@ -1834,6 +1896,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="J18" s="10"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
@@ -1847,6 +1910,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="J19" s="10"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
@@ -1860,6 +1924,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="J20" s="10"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
@@ -1873,6 +1938,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="J21" s="10"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="2">

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA9544E-9EC5-4DBB-A92C-B0BFA15FA297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF81303E-0318-4EC4-AB43-9209CAF171BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1485" yWindow="4755" windowWidth="34110" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="46">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -215,6 +215,14 @@
   </si>
   <si>
     <t>压缩饼干吃起来还行，吃完了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午15+晚上12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午15+晚上13</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1488,7 +1496,10 @@
       <c r="D2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="3"/>
+      <c r="E2" s="3">
+        <f>B2-C2</f>
+        <v>1</v>
+      </c>
       <c r="F2" s="3"/>
       <c r="G2" s="1"/>
       <c r="H2" s="6">
@@ -1506,7 +1517,7 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>93.8</v>
+        <v>148.80000000000001</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
@@ -1541,11 +1552,14 @@
       <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1"/>
+      <c r="E3" s="3">
+        <f t="shared" ref="E3:E33" si="0">B3-C3</f>
+        <v>1</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="6">
-        <f t="shared" ref="H3:H34" si="0">SUM(C3,F3)</f>
+        <f t="shared" ref="H3:H34" si="1">SUM(C3,F3)</f>
         <v>10</v>
       </c>
       <c r="J3" s="1"/>
@@ -1573,13 +1587,16 @@
       <c r="D4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H4" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -1608,7 +1625,10 @@
       <c r="D5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="1"/>
+      <c r="E5" s="3">
+        <f t="shared" si="0"/>
+        <v>2.1999999999999993</v>
+      </c>
       <c r="F5" s="9">
         <v>13.9</v>
       </c>
@@ -1616,7 +1636,7 @@
         <v>34</v>
       </c>
       <c r="H5" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22.700000000000003</v>
       </c>
       <c r="J5" s="9">
@@ -1639,7 +1659,10 @@
       <c r="D6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="F6" s="9">
         <f>7.39+4.3+11.9</f>
         <v>23.59</v>
@@ -1648,7 +1671,7 @@
         <v>35</v>
       </c>
       <c r="H6" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>23.59</v>
       </c>
       <c r="J6" s="9">
@@ -1671,7 +1694,10 @@
       <c r="D7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="1"/>
+      <c r="E7" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="F7" s="9">
         <f>3.81+7.6</f>
         <v>11.41</v>
@@ -1680,7 +1706,7 @@
         <v>39</v>
       </c>
       <c r="H7" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>21.41</v>
       </c>
       <c r="J7" s="9">
@@ -1703,11 +1729,14 @@
       <c r="D8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="1"/>
+      <c r="E8" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J8" s="9"/>
@@ -1726,11 +1755,14 @@
       <c r="D9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="1"/>
+      <c r="E9" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J9" s="9"/>
@@ -1749,11 +1781,14 @@
       <c r="D10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="1"/>
+      <c r="E10" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J10" s="9"/>
@@ -1772,11 +1807,14 @@
       <c r="D11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="1"/>
+      <c r="E11" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J11" s="9"/>
@@ -1795,11 +1833,14 @@
       <c r="D12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="1"/>
+      <c r="E12" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="J12" s="9"/>
@@ -1818,11 +1859,14 @@
       <c r="D13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="1"/>
+      <c r="E13" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J13" s="9"/>
@@ -1835,10 +1879,19 @@
       <c r="B14" s="3">
         <v>11</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="10">
+        <v>27</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="0"/>
+        <v>-16</v>
+      </c>
       <c r="H14" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>27</v>
       </c>
       <c r="J14" s="10"/>
     </row>
@@ -1849,10 +1902,19 @@
       <c r="B15" s="3">
         <v>11</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="10">
+        <v>28</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="0"/>
+        <v>-17</v>
+      </c>
       <c r="H15" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1864,8 +1926,12 @@
         <v>11</v>
       </c>
       <c r="C16" s="10"/>
+      <c r="E16" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="H16" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J16" s="10"/>
@@ -1878,8 +1944,12 @@
         <v>11</v>
       </c>
       <c r="C17" s="10"/>
+      <c r="E17" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="H17" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J17" s="10"/>
@@ -1892,8 +1962,12 @@
         <v>11</v>
       </c>
       <c r="C18" s="10"/>
+      <c r="E18" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="H18" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J18" s="10"/>
@@ -1906,8 +1980,12 @@
         <v>11</v>
       </c>
       <c r="C19" s="10"/>
+      <c r="E19" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="H19" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J19" s="10"/>
@@ -1920,8 +1998,12 @@
         <v>11</v>
       </c>
       <c r="C20" s="10"/>
+      <c r="E20" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="H20" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J20" s="10"/>
@@ -1934,8 +2016,12 @@
         <v>11</v>
       </c>
       <c r="C21" s="10"/>
+      <c r="E21" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="H21" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J21" s="10"/>
@@ -1948,8 +2034,12 @@
         <v>11</v>
       </c>
       <c r="C22" s="10"/>
+      <c r="E22" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="H22" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1961,8 +2051,12 @@
         <v>11</v>
       </c>
       <c r="C23" s="10"/>
+      <c r="E23" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="H23" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1974,8 +2068,12 @@
         <v>11</v>
       </c>
       <c r="C24" s="10"/>
+      <c r="E24" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="H24" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1987,8 +2085,12 @@
         <v>11</v>
       </c>
       <c r="C25" s="10"/>
+      <c r="E25" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="H25" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2000,8 +2102,12 @@
         <v>11</v>
       </c>
       <c r="C26" s="10"/>
+      <c r="E26" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="H26" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2013,8 +2119,12 @@
         <v>11</v>
       </c>
       <c r="C27" s="10"/>
+      <c r="E27" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="H27" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2026,8 +2136,12 @@
         <v>11</v>
       </c>
       <c r="C28" s="10"/>
+      <c r="E28" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="H28" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2039,8 +2153,12 @@
         <v>11</v>
       </c>
       <c r="C29" s="10"/>
+      <c r="E29" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="H29" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2052,8 +2170,12 @@
         <v>11</v>
       </c>
       <c r="C30" s="10"/>
+      <c r="E30" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="H30" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2066,11 +2188,14 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
+      <c r="E31" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I31" s="1"/>
@@ -2083,19 +2208,26 @@
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+      <c r="E32" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E33" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H33" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I33" s="1"/>
@@ -2103,7 +2235,7 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H34" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I34" s="1"/>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF81303E-0318-4EC4-AB43-9209CAF171BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB3C2A4-2B46-4953-9172-ED89AE94F14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="51">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -223,6 +223,26 @@
   </si>
   <si>
     <t>中午15+晚上13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午15+晚上15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>千层糕 13+ 鸡心 7.57</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> up鹿头军事充电 18</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午13.7+晚上12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>麦片</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1410,7 +1430,7 @@
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="53.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.875" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="27.625" bestFit="1" customWidth="1"/>
@@ -1517,11 +1537,11 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>148.80000000000001</v>
+        <v>224.5</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
-        <v>48.900000000000006</v>
+        <v>87.47</v>
       </c>
       <c r="N2" s="3">
         <v>300</v>
@@ -1532,7 +1552,7 @@
       </c>
       <c r="P2" s="3">
         <f>SUM(N2:O2)-M2+SUM(J5:J35)</f>
-        <v>271.10000000000002</v>
+        <v>232.53</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="1"/>
@@ -1733,7 +1753,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F8" s="1"/>
+      <c r="F8" s="9"/>
       <c r="G8" s="1"/>
       <c r="H8" s="6">
         <f t="shared" si="1"/>
@@ -1759,7 +1779,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F9" s="1"/>
+      <c r="F9" s="9"/>
       <c r="G9" s="1"/>
       <c r="H9" s="6">
         <f t="shared" si="1"/>
@@ -1785,7 +1805,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F10" s="1"/>
+      <c r="F10" s="9"/>
       <c r="G10" s="1"/>
       <c r="H10" s="6">
         <f t="shared" si="1"/>
@@ -1811,7 +1831,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F11" s="1"/>
+      <c r="F11" s="9"/>
       <c r="G11" s="1"/>
       <c r="H11" s="6">
         <f t="shared" si="1"/>
@@ -1837,7 +1857,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F12" s="1"/>
+      <c r="F12" s="9"/>
       <c r="G12" s="1"/>
       <c r="H12" s="6">
         <f t="shared" si="1"/>
@@ -1863,7 +1883,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F13" s="1"/>
+      <c r="F13" s="9"/>
       <c r="G13" s="1"/>
       <c r="H13" s="6">
         <f t="shared" si="1"/>
@@ -1889,6 +1909,7 @@
         <f t="shared" si="0"/>
         <v>-16</v>
       </c>
+      <c r="F14" s="10"/>
       <c r="H14" s="6">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -1912,6 +1933,7 @@
         <f t="shared" si="0"/>
         <v>-17</v>
       </c>
+      <c r="F15" s="10"/>
       <c r="H15" s="6">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -1925,14 +1947,20 @@
       <c r="B16" s="3">
         <v>11</v>
       </c>
-      <c r="C16" s="10"/>
+      <c r="C16" s="10">
+        <v>30</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
+        <v>-19</v>
+      </c>
+      <c r="F16" s="10"/>
       <c r="H16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J16" s="10"/>
     </row>
@@ -1943,14 +1971,27 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="10"/>
+      <c r="C17" s="10">
+        <f>13.7+12</f>
+        <v>25.7</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>-14.7</v>
+      </c>
+      <c r="F17" s="10">
+        <f>13+7.57</f>
+        <v>20.57</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="H17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(C17,F17)</f>
+        <v>46.269999999999996</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1961,14 +2002,19 @@
       <c r="B18" s="3">
         <v>11</v>
       </c>
-      <c r="C18" s="10"/>
+      <c r="C18" s="10">
+        <v>10</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(C18,F18)</f>
+        <v>10</v>
       </c>
       <c r="J18" s="10"/>
     </row>
@@ -1979,14 +2025,25 @@
       <c r="B19" s="3">
         <v>11</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="10">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="F19" s="10">
+        <v>18</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="H19" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(C19,F19)</f>
+        <v>18</v>
       </c>
       <c r="J19" s="10"/>
     </row>
@@ -1997,14 +2054,20 @@
       <c r="B20" s="3">
         <v>11</v>
       </c>
-      <c r="C20" s="10"/>
+      <c r="C20" s="10">
+        <v>10</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F20" s="10"/>
       <c r="H20" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J20" s="10"/>
     </row>
@@ -2020,6 +2083,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="F21" s="10"/>
       <c r="H21" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2038,6 +2102,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="F22" s="10"/>
       <c r="H22" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2055,6 +2120,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="F23" s="10"/>
       <c r="H23" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2072,6 +2138,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="F24" s="10"/>
       <c r="H24" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2089,6 +2156,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="F25" s="10"/>
       <c r="H25" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2106,6 +2174,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="F26" s="10"/>
       <c r="H26" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2123,6 +2192,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="F27" s="10"/>
       <c r="H27" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2140,6 +2210,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="F28" s="10"/>
       <c r="H28" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2157,6 +2228,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="F29" s="10"/>
       <c r="H29" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2174,6 +2246,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="F30" s="10"/>
       <c r="H30" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2192,7 +2265,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F31" s="1"/>
+      <c r="F31" s="9"/>
       <c r="G31" s="1"/>
       <c r="H31" s="6">
         <f t="shared" si="1"/>
@@ -2212,7 +2285,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F32" s="1"/>
+      <c r="F32" s="9"/>
       <c r="G32" s="1"/>
       <c r="H32" s="6">
         <f t="shared" si="1"/>
@@ -2226,6 +2299,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="F33" s="10"/>
       <c r="H33" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2234,6 +2308,7 @@
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="F34" s="10"/>
       <c r="H34" s="6">
         <f t="shared" si="1"/>
         <v>0</v>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB3C2A4-2B46-4953-9172-ED89AE94F14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42E48F7-C34F-48E0-9391-117B91CEF952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -243,6 +243,14 @@
   </si>
   <si>
     <t>麦片</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>盐酸苯海拉明片 18.5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1537,11 +1545,11 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>224.5</v>
+        <v>279.5</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
-        <v>87.47</v>
+        <v>105.97</v>
       </c>
       <c r="N2" s="3">
         <v>300</v>
@@ -1552,7 +1560,7 @@
       </c>
       <c r="P2" s="3">
         <f>SUM(N2:O2)-M2+SUM(J5:J35)</f>
-        <v>232.53</v>
+        <v>214.03</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="1"/>
@@ -2078,15 +2086,20 @@
       <c r="B21" s="3">
         <v>11</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="10">
+        <v>10</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F21" s="10"/>
       <c r="H21" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J21" s="10"/>
     </row>
@@ -2097,15 +2110,20 @@
       <c r="B22" s="3">
         <v>11</v>
       </c>
-      <c r="C22" s="10"/>
+      <c r="C22" s="10">
+        <v>10</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F22" s="10"/>
       <c r="H22" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -2115,15 +2133,20 @@
       <c r="B23" s="3">
         <v>11</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="10">
+        <v>10</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F23" s="10"/>
       <c r="H23" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -2133,15 +2156,20 @@
       <c r="B24" s="3">
         <v>11</v>
       </c>
-      <c r="C24" s="10"/>
+      <c r="C24" s="10">
+        <v>10</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E24" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F24" s="10"/>
       <c r="H24" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -2151,15 +2179,26 @@
       <c r="B25" s="3">
         <v>11</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="10">
+        <v>10</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="F25" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="F25" s="10">
+        <f>18.5</f>
+        <v>18.5</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="H25" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -2169,15 +2208,20 @@
       <c r="B26" s="3">
         <v>11</v>
       </c>
-      <c r="C26" s="10"/>
+      <c r="C26" s="10">
+        <v>5</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F26" s="10"/>
       <c r="H26" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42E48F7-C34F-48E0-9391-117B91CEF952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5D2957-2FCC-4AD2-A4FB-302D9BFEFA59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="55">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -251,6 +251,14 @@
   </si>
   <si>
     <t>盐酸苯海拉明片 18.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚上 8.8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">两短袖 49+俩裤子73+鱼干 10 + 豆罐头 10.5 +猪肘 3.2 + 车票 10 + 电动牙刷 78.66 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1438,7 +1446,7 @@
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="53.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.125" style="7" customWidth="1"/>
     <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="27.625" bestFit="1" customWidth="1"/>
@@ -1448,7 +1456,8 @@
     <col min="16" max="16" width="13" customWidth="1"/>
     <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
@@ -1545,11 +1554,11 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>279.5</v>
+        <v>288.3</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
-        <v>105.97</v>
+        <v>340.33</v>
       </c>
       <c r="N2" s="3">
         <v>300</v>
@@ -1560,12 +1569,15 @@
       </c>
       <c r="P2" s="3">
         <f>SUM(N2:O2)-M2+SUM(J5:J35)</f>
-        <v>214.03</v>
+        <v>-20.329999999999984</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
+      <c r="T2" s="3">
+        <f xml:space="preserve"> SUM(H2:H34)</f>
+        <v>628.63</v>
+      </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
@@ -2231,15 +2243,26 @@
       <c r="B27" s="3">
         <v>11</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="10">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="F27" s="10"/>
+        <v>2.1999999999999993</v>
+      </c>
+      <c r="F27" s="10">
+        <f>49+73+10+10.5+3.2+10+78.66</f>
+        <v>234.35999999999999</v>
+      </c>
+      <c r="G27" t="s">
+        <v>54</v>
+      </c>
       <c r="H27" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(C27,F27)</f>
+        <v>243.16</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5D2957-2FCC-4AD2-A4FB-302D9BFEFA59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D56A5C-D129-4EFC-910A-CC57F00B09FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5205" yWindow="675" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="58">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -259,6 +259,18 @@
   </si>
   <si>
     <t xml:space="preserve">两短袖 49+俩裤子73+鱼干 10 + 豆罐头 10.5 +猪肘 3.2 + 车票 10 + 电动牙刷 78.66 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>牙膏 22.7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">hdmi 16.4 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雨伞 13.52</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1554,11 +1566,11 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>288.3</v>
+        <v>308.3</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
-        <v>340.33</v>
+        <v>392.94999999999993</v>
       </c>
       <c r="N2" s="3">
         <v>300</v>
@@ -1569,14 +1581,14 @@
       </c>
       <c r="P2" s="3">
         <f>SUM(N2:O2)-M2+SUM(J5:J35)</f>
-        <v>-20.329999999999984</v>
+        <v>-72.949999999999932</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="3">
         <f xml:space="preserve"> SUM(H2:H34)</f>
-        <v>628.63</v>
+        <v>701.25</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
@@ -2272,15 +2284,25 @@
       <c r="B28" s="3">
         <v>11</v>
       </c>
-      <c r="C28" s="10"/>
+      <c r="C28" s="10">
+        <v>10</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="F28" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="F28" s="10">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="H28" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -2290,15 +2312,25 @@
       <c r="B29" s="3">
         <v>11</v>
       </c>
-      <c r="C29" s="10"/>
+      <c r="C29" s="10">
+        <v>10</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="F29" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="F29" s="10">
+        <v>22.7</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="H29" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>32.700000000000003</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
@@ -2313,10 +2345,15 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F30" s="10"/>
+      <c r="F30" s="10">
+        <v>13.52</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="H30" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D56A5C-D129-4EFC-910A-CC57F00B09FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF987FFD-986B-497B-BE67-8867C0C062D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5205" yWindow="675" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6750" yWindow="1485" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
     <sheet name="四月" sheetId="2" r:id="rId2"/>
+    <sheet name="五月" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -271,6 +272,26 @@
   </si>
   <si>
     <t>雨伞 13.52</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅菜扣肉小点心10.7+ 小鱼干 13.4 + 铝罐子 4.77 + 茶氨酸 4.83</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛋糕全部吃完，奶油味道很不错</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>类目</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>千层糕 13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">雨伞 17 + 对乙酰氨基酚片 0.5 + 枣糕 6.8 +各类水果 13 + 吐司面包 13+ 花生 5.88 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1566,7 +1587,7 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>308.3</v>
+        <v>323.3</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
@@ -1588,7 +1609,7 @@
       <c r="S2" s="1"/>
       <c r="T2" s="3">
         <f xml:space="preserve"> SUM(H2:H34)</f>
-        <v>701.25</v>
+        <v>716.25</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
@@ -2340,10 +2361,15 @@
       <c r="B30" s="3">
         <v>11</v>
       </c>
-      <c r="C30" s="10"/>
+      <c r="C30" s="10">
+        <v>10</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F30" s="10">
         <v>13.52</v>
@@ -2353,7 +2379,7 @@
       </c>
       <c r="H30" s="6">
         <f t="shared" si="1"/>
-        <v>13.52</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
@@ -2363,25 +2389,25 @@
       <c r="B31" s="3">
         <v>11</v>
       </c>
-      <c r="C31" s="9"/>
+      <c r="C31" s="9">
+        <v>5</v>
+      </c>
       <c r="D31" s="1"/>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="1"/>
       <c r="H31" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" s="2">
-        <v>46143</v>
-      </c>
+      <c r="A32" s="2"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -2516,4 +2542,955 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2823FC-8AAF-4CEF-978E-171470B39C64}">
+  <dimension ref="A1:U43"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="53.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" customWidth="1"/>
+    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B2" s="3">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3">
+        <f>B2-C2</f>
+        <v>11</v>
+      </c>
+      <c r="F2" s="3">
+        <f>10.7+ 13.4 +4.77 +4.83</f>
+        <v>33.700000000000003</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="6">
+        <f>SUM(C2,F2)</f>
+        <v>33.700000000000003</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="3">
+        <f>AVERAGE(B2:B32)</f>
+        <v>11</v>
+      </c>
+      <c r="K2" s="3">
+        <f>SUM(B2:B31)</f>
+        <v>330</v>
+      </c>
+      <c r="L2" s="3">
+        <f>SUM(C2:C32)</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="3">
+        <f>SUM(F2:F32)</f>
+        <v>89.88</v>
+      </c>
+      <c r="N2" s="3">
+        <v>200</v>
+      </c>
+      <c r="O2" s="3">
+        <f>SUM(J5:J48)</f>
+        <v>10</v>
+      </c>
+      <c r="P2" s="3">
+        <f>SUM(N2:O2)-M2+SUM(J5:J35)</f>
+        <v>130.12</v>
+      </c>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="3">
+        <f xml:space="preserve"> SUM(H2:H34)</f>
+        <v>89.88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>46144</v>
+      </c>
+      <c r="B3" s="3">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3">
+        <f t="shared" ref="E3:E33" si="0">B3-C3</f>
+        <v>11</v>
+      </c>
+      <c r="F3" s="9">
+        <f>17 + 0.5 +6.8 + 13 +  13+5.88</f>
+        <v>56.18</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="6">
+        <f t="shared" ref="H3:H34" si="1">SUM(C3,F3)</f>
+        <v>56.18</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>46145</v>
+      </c>
+      <c r="B4" s="3">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B5" s="3">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="9">
+        <v>10</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>46147</v>
+      </c>
+      <c r="B6" s="3">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B7" s="3">
+        <v>11</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="9"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B8" s="3">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B9" s="3">
+        <v>11</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>46151</v>
+      </c>
+      <c r="B10" s="3">
+        <v>11</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="9"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>46152</v>
+      </c>
+      <c r="B11" s="3">
+        <v>11</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="9"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B12" s="3">
+        <v>11</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="9"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B13" s="3">
+        <v>11</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="9"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B14" s="3">
+        <v>11</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="H14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="10"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>46156</v>
+      </c>
+      <c r="B15" s="3">
+        <v>11</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="H15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="10"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B16" s="3">
+        <v>11</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="H16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="10"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>46158</v>
+      </c>
+      <c r="B17" s="3">
+        <v>11</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F17" s="10"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="6">
+        <f>SUM(C17,F17)</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="10"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>46159</v>
+      </c>
+      <c r="B18" s="3">
+        <v>11</v>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="H18" s="6">
+        <f>SUM(C18,F18)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="10"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B19" s="3">
+        <v>11</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F19" s="10"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="6">
+        <f>SUM(C19,F19)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="10"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>46161</v>
+      </c>
+      <c r="B20" s="3">
+        <v>11</v>
+      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="H20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="10"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B21" s="3">
+        <v>11</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F21" s="10"/>
+      <c r="H21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="10"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B22" s="3">
+        <v>11</v>
+      </c>
+      <c r="C22" s="10"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F22" s="10"/>
+      <c r="H22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B23" s="3">
+        <v>11</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="H23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B24" s="3">
+        <v>11</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F24" s="10"/>
+      <c r="H24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B25" s="3">
+        <v>11</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F25" s="10"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B26" s="3">
+        <v>11</v>
+      </c>
+      <c r="C26" s="10"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F26" s="10"/>
+      <c r="H26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B27" s="3">
+        <v>11</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F27" s="10"/>
+      <c r="H27" s="6">
+        <f>SUM(C27,F27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B28" s="3">
+        <v>11</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F28" s="10"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>46170</v>
+      </c>
+      <c r="B29" s="3">
+        <v>11</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F29" s="10"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B30" s="3">
+        <v>11</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="E30" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F30" s="10"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B31" s="3">
+        <v>11</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>46173</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="9"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="2"/>
+      <c r="E33" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="10"/>
+      <c r="H33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" s="2"/>
+      <c r="F34" s="10"/>
+      <c r="H34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="2"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" s="2"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" s="2"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="2"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF987FFD-986B-497B-BE67-8867C0C062D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7551D9-3CE8-40E7-9C00-2941CB0AAF3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6750" yWindow="1485" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="64">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -292,6 +292,10 @@
   </si>
   <si>
     <t xml:space="preserve">雨伞 17 + 对乙酰氨基酚片 0.5 + 枣糕 6.8 +各类水果 13 + 吐司面包 13+ 花生 5.88 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">瓜拉纳提取物100g 9.30 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2664,11 +2668,11 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
-        <v>89.88</v>
+        <v>99.179999999999993</v>
       </c>
       <c r="N2" s="3">
         <v>200</v>
@@ -2679,14 +2683,14 @@
       </c>
       <c r="P2" s="3">
         <f>SUM(N2:O2)-M2+SUM(J5:J35)</f>
-        <v>130.12</v>
+        <v>120.82000000000001</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="3">
         <f xml:space="preserve"> SUM(H2:H34)</f>
-        <v>89.88</v>
+        <v>131.18</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
@@ -2831,17 +2835,23 @@
       <c r="B7" s="3">
         <v>11</v>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3">
+        <v>10</v>
+      </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="F7" s="9">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="H7" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="1"/>
@@ -2856,17 +2866,19 @@
       <c r="B8" s="3">
         <v>11</v>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3">
+        <v>11</v>
+      </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="1"/>
       <c r="H8" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="1"/>
@@ -2881,17 +2893,19 @@
       <c r="B9" s="3">
         <v>11</v>
       </c>
-      <c r="C9" s="9"/>
+      <c r="C9" s="3">
+        <v>11</v>
+      </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="1"/>
       <c r="H9" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="1"/>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7551D9-3CE8-40E7-9C00-2941CB0AAF3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4E2D8D-B52C-4D13-BC87-D729D9C411F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
@@ -2690,7 +2690,7 @@
       <c r="S2" s="1"/>
       <c r="T2" s="3">
         <f xml:space="preserve"> SUM(H2:H34)</f>
-        <v>131.18</v>
+        <v>137.18</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
@@ -2920,17 +2920,19 @@
       <c r="B10" s="3">
         <v>11</v>
       </c>
-      <c r="C10" s="9"/>
+      <c r="C10" s="9">
+        <v>6</v>
+      </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="1"/>
       <c r="H10" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J10" s="9"/>
       <c r="K10" s="1"/>
@@ -2945,7 +2947,9 @@
       <c r="B11" s="3">
         <v>11</v>
       </c>
-      <c r="C11" s="9"/>
+      <c r="C11" s="9">
+        <v>0</v>
+      </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3">
         <f t="shared" si="0"/>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4E2D8D-B52C-4D13-BC87-D729D9C411F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75D219E-E69E-43EB-89CF-AD2BFD5CAC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
@@ -2690,7 +2690,7 @@
       <c r="S2" s="1"/>
       <c r="T2" s="3">
         <f xml:space="preserve"> SUM(H2:H34)</f>
-        <v>137.18</v>
+        <v>147.18</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
@@ -2974,17 +2974,19 @@
       <c r="B12" s="3">
         <v>11</v>
       </c>
-      <c r="C12" s="9"/>
+      <c r="C12" s="9">
+        <v>10</v>
+      </c>
       <c r="D12" s="1"/>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F12" s="9"/>
       <c r="G12" s="1"/>
       <c r="H12" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="9"/>
     </row>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75D219E-E69E-43EB-89CF-AD2BFD5CAC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9F8610-D0C6-487B-801B-F2D1807ADB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2760" yWindow="1770" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
@@ -2690,7 +2690,7 @@
       <c r="S2" s="1"/>
       <c r="T2" s="3">
         <f xml:space="preserve"> SUM(H2:H34)</f>
-        <v>147.18</v>
+        <v>157.18</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
@@ -2997,17 +2997,19 @@
       <c r="B13" s="3">
         <v>11</v>
       </c>
-      <c r="C13" s="9"/>
+      <c r="C13" s="9">
+        <v>10</v>
+      </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="1"/>
       <c r="H13" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J13" s="9"/>
     </row>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9F8610-D0C6-487B-801B-F2D1807ADB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3680C9F4-5868-4CC9-B39A-F377A443AD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="1770" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="66">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -296,6 +296,14 @@
   </si>
   <si>
     <t xml:space="preserve">瓜拉纳提取物100g 9.30 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 域名购置 12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>服务器购置 68</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2415,10 +2423,7 @@
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="E32" s="3"/>
       <c r="F32" s="9"/>
       <c r="G32" s="1"/>
       <c r="H32" s="6">
@@ -2429,10 +2434,7 @@
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="E33" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="E33" s="3"/>
       <c r="F33" s="10"/>
       <c r="H33" s="6">
         <f t="shared" si="1"/>
@@ -2556,7 +2558,7 @@
     <col min="1" max="1" width="14.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="53.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="75.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.125" style="7" customWidth="1"/>
     <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
@@ -2668,11 +2670,11 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
-        <v>99.179999999999993</v>
+        <v>179.18</v>
       </c>
       <c r="N2" s="3">
         <v>200</v>
@@ -2683,14 +2685,14 @@
       </c>
       <c r="P2" s="3">
         <f>SUM(N2:O2)-M2+SUM(J5:J35)</f>
-        <v>120.82000000000001</v>
+        <v>40.819999999999993</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="3">
         <f xml:space="preserve"> SUM(H2:H34)</f>
-        <v>157.18</v>
+        <v>284.18</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
@@ -2874,11 +2876,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="1"/>
+      <c r="F8" s="9">
+        <v>12</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="H8" s="6">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="1"/>
@@ -2929,7 +2935,6 @@
         <v>5</v>
       </c>
       <c r="F10" s="9"/>
-      <c r="G10" s="1"/>
       <c r="H10" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -2982,11 +2987,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="1"/>
+      <c r="F12" s="9">
+        <v>68</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="H12" s="6">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="J12" s="9"/>
     </row>
@@ -3020,16 +3029,18 @@
       <c r="B14" s="3">
         <v>11</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="10">
+        <v>11</v>
+      </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F14" s="10"/>
       <c r="H14" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J14" s="10"/>
     </row>
@@ -3040,16 +3051,18 @@
       <c r="B15" s="3">
         <v>11</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="10">
+        <v>13</v>
+      </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>-2</v>
       </c>
       <c r="F15" s="10"/>
       <c r="H15" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -3060,16 +3073,18 @@
       <c r="B16" s="3">
         <v>11</v>
       </c>
-      <c r="C16" s="10"/>
+      <c r="C16" s="10">
+        <v>10</v>
+      </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F16" s="10"/>
       <c r="H16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J16" s="10"/>
     </row>
@@ -3080,7 +3095,9 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="10"/>
+      <c r="C17" s="10">
+        <v>0</v>
+      </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
@@ -3101,7 +3118,9 @@
       <c r="B18" s="3">
         <v>11</v>
       </c>
-      <c r="C18" s="10"/>
+      <c r="C18" s="10">
+        <v>0</v>
+      </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
@@ -3121,17 +3140,19 @@
       <c r="B19" s="3">
         <v>11</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="10">
+        <v>13</v>
+      </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>-2</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="1"/>
       <c r="H19" s="6">
         <f>SUM(C19,F19)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J19" s="10"/>
     </row>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3680C9F4-5868-4CC9-B39A-F377A443AD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EDBEE0-770D-4E63-A74C-08EE0A59856E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="67">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -304,6 +304,10 @@
   </si>
   <si>
     <t>服务器购置 68</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>网易云会员 50</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1638,7 +1642,7 @@
         <v>15</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E33" si="0">B3-C3</f>
+        <f t="shared" ref="E3:E31" si="0">B3-C3</f>
         <v>1</v>
       </c>
       <c r="F3" s="1"/>
@@ -2552,25 +2556,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2823FC-8AAF-4CEF-978E-171470B39C64}">
-  <dimension ref="A1:U43"/>
+  <dimension ref="A1:U38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="75.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.125" style="7" customWidth="1"/>
-    <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="30.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="75.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" style="1"/>
+    <col min="20" max="20" width="8.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
@@ -2619,7 +2627,6 @@
       <c r="P1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="1"/>
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
@@ -2659,7 +2666,7 @@
         <f>SUM(C2,F2)</f>
         <v>33.700000000000003</v>
       </c>
-      <c r="I2" s="4"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="3">
         <f>AVERAGE(B2:B32)</f>
         <v>11</v>
@@ -2670,7 +2677,7 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
@@ -2688,11 +2695,9 @@
         <v>40.819999999999993</v>
       </c>
       <c r="Q2" s="3"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
       <c r="T2" s="3">
         <f xml:space="preserve"> SUM(H2:H34)</f>
-        <v>284.18</v>
+        <v>305.18</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
@@ -2721,17 +2726,6 @@
         <f t="shared" ref="H3:H34" si="1">SUM(C3,F3)</f>
         <v>56.18</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
@@ -2743,13 +2737,11 @@
       <c r="C4" s="3">
         <v>0</v>
       </c>
-      <c r="D4" s="1"/>
       <c r="E4" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="F4" s="9"/>
-      <c r="G4" s="1"/>
       <c r="H4" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2780,13 +2772,11 @@
       <c r="C5" s="3">
         <v>0</v>
       </c>
-      <c r="D5" s="1"/>
       <c r="E5" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="F5" s="9"/>
-      <c r="G5" s="1"/>
       <c r="H5" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2800,8 +2790,6 @@
       <c r="L5" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
@@ -2813,22 +2801,16 @@
       <c r="C6" s="3">
         <v>0</v>
       </c>
-      <c r="D6" s="1"/>
       <c r="E6" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="F6" s="9"/>
-      <c r="G6" s="1"/>
       <c r="H6" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J6" s="9"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
@@ -2856,10 +2838,6 @@
         <v>19.3</v>
       </c>
       <c r="J7" s="9"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
@@ -2887,10 +2865,6 @@
         <v>23</v>
       </c>
       <c r="J8" s="9"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
@@ -2908,16 +2882,11 @@
         <v>0</v>
       </c>
       <c r="F9" s="9"/>
-      <c r="G9" s="1"/>
       <c r="H9" s="6">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="J9" s="9"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
@@ -2940,10 +2909,6 @@
         <v>6</v>
       </c>
       <c r="J10" s="9"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
@@ -2961,16 +2926,11 @@
         <v>11</v>
       </c>
       <c r="F11" s="9"/>
-      <c r="G11" s="1"/>
       <c r="H11" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J11" s="9"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
@@ -2982,7 +2942,6 @@
       <c r="C12" s="9">
         <v>10</v>
       </c>
-      <c r="D12" s="1"/>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -3015,7 +2974,6 @@
         <v>1</v>
       </c>
       <c r="F13" s="9"/>
-      <c r="G13" s="1"/>
       <c r="H13" s="6">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -3029,7 +2987,7 @@
       <c r="B14" s="3">
         <v>11</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <v>11</v>
       </c>
       <c r="D14" s="3"/>
@@ -3037,12 +2995,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F14" s="10"/>
+      <c r="F14" s="9"/>
       <c r="H14" s="6">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="J14" s="10"/>
+      <c r="J14" s="9"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
@@ -3051,7 +3009,7 @@
       <c r="B15" s="3">
         <v>11</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <v>13</v>
       </c>
       <c r="D15" s="3"/>
@@ -3059,12 +3017,12 @@
         <f t="shared" si="0"/>
         <v>-2</v>
       </c>
-      <c r="F15" s="10"/>
+      <c r="F15" s="9"/>
       <c r="H15" s="6">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="J15" s="10"/>
+      <c r="J15" s="9"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
@@ -3073,7 +3031,7 @@
       <c r="B16" s="3">
         <v>11</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <v>10</v>
       </c>
       <c r="D16" s="3"/>
@@ -3081,12 +3039,12 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F16" s="10"/>
+      <c r="F16" s="9"/>
       <c r="H16" s="6">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J16" s="10"/>
+      <c r="J16" s="9"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
@@ -3095,7 +3053,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <v>0</v>
       </c>
       <c r="D17" s="3"/>
@@ -3103,13 +3061,12 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="1"/>
+      <c r="F17" s="9"/>
       <c r="H17" s="6">
         <f>SUM(C17,F17)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="10"/>
+      <c r="J17" s="9"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
@@ -3118,7 +3075,7 @@
       <c r="B18" s="3">
         <v>11</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <v>0</v>
       </c>
       <c r="D18" s="3"/>
@@ -3126,12 +3083,12 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F18" s="10"/>
+      <c r="F18" s="9"/>
       <c r="H18" s="6">
         <f>SUM(C18,F18)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="10"/>
+      <c r="J18" s="9"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
@@ -3140,7 +3097,7 @@
       <c r="B19" s="3">
         <v>11</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <v>13</v>
       </c>
       <c r="D19" s="3"/>
@@ -3148,13 +3105,12 @@
         <f t="shared" si="0"/>
         <v>-2</v>
       </c>
-      <c r="F19" s="10"/>
-      <c r="G19" s="1"/>
+      <c r="F19" s="9"/>
       <c r="H19" s="6">
         <f>SUM(C19,F19)</f>
         <v>13</v>
       </c>
-      <c r="J19" s="10"/>
+      <c r="J19" s="9"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
@@ -3163,18 +3119,20 @@
       <c r="B20" s="3">
         <v>11</v>
       </c>
-      <c r="C20" s="10"/>
+      <c r="C20" s="9">
+        <v>10</v>
+      </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="F20" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="F20" s="9"/>
       <c r="H20" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="10"/>
+        <v>10</v>
+      </c>
+      <c r="J20" s="9"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
@@ -3183,18 +3141,23 @@
       <c r="B21" s="3">
         <v>11</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="9">
+        <v>11</v>
+      </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="F21" s="10"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="9"/>
+      <c r="G21" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="H21" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="10"/>
+        <v>11</v>
+      </c>
+      <c r="J21" s="9"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
@@ -3203,13 +3166,13 @@
       <c r="B22" s="3">
         <v>11</v>
       </c>
-      <c r="C22" s="10"/>
+      <c r="C22" s="9"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F22" s="10"/>
+      <c r="F22" s="9"/>
       <c r="H22" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3222,13 +3185,13 @@
       <c r="B23" s="3">
         <v>11</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F23" s="10"/>
+      <c r="F23" s="9"/>
       <c r="H23" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3241,13 +3204,13 @@
       <c r="B24" s="3">
         <v>11</v>
       </c>
-      <c r="C24" s="10"/>
+      <c r="C24" s="9"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F24" s="10"/>
+      <c r="F24" s="9"/>
       <c r="H24" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3260,14 +3223,13 @@
       <c r="B25" s="3">
         <v>11</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="1"/>
+      <c r="F25" s="9"/>
       <c r="H25" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3280,13 +3242,13 @@
       <c r="B26" s="3">
         <v>11</v>
       </c>
-      <c r="C26" s="10"/>
+      <c r="C26" s="9"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F26" s="10"/>
+      <c r="F26" s="9"/>
       <c r="H26" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3299,13 +3261,13 @@
       <c r="B27" s="3">
         <v>11</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="9"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F27" s="10"/>
+      <c r="F27" s="9"/>
       <c r="H27" s="6">
         <f>SUM(C27,F27)</f>
         <v>0</v>
@@ -3318,14 +3280,13 @@
       <c r="B28" s="3">
         <v>11</v>
       </c>
-      <c r="C28" s="10"/>
+      <c r="C28" s="9"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F28" s="10"/>
-      <c r="G28" s="1"/>
+      <c r="F28" s="9"/>
       <c r="H28" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3338,14 +3299,13 @@
       <c r="B29" s="3">
         <v>11</v>
       </c>
-      <c r="C29" s="10"/>
+      <c r="C29" s="9"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F29" s="10"/>
-      <c r="G29" s="1"/>
+      <c r="F29" s="9"/>
       <c r="H29" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3358,13 +3318,12 @@
       <c r="B30" s="3">
         <v>11</v>
       </c>
-      <c r="C30" s="10"/>
+      <c r="C30" s="9"/>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F30" s="10"/>
-      <c r="G30" s="1"/>
+      <c r="F30" s="9"/>
       <c r="H30" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3378,159 +3337,61 @@
         <v>11</v>
       </c>
       <c r="C31" s="9"/>
-      <c r="D31" s="1"/>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="F31" s="9"/>
-      <c r="G31" s="1"/>
       <c r="H31" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>46173</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F32" s="9"/>
-      <c r="G32" s="1"/>
       <c r="H32" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F33" s="10"/>
+      <c r="F33" s="9"/>
       <c r="H33" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
-      <c r="F34" s="10"/>
+      <c r="F34" s="9"/>
       <c r="H34" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EDBEE0-770D-4E63-A74C-08EE0A59856E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478E7998-17DB-4A56-B781-4C7B40B30760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2677,11 +2677,11 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
-        <v>179.18</v>
+        <v>229.18</v>
       </c>
       <c r="N2" s="3">
         <v>200</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="P2" s="3">
         <f>SUM(N2:O2)-M2+SUM(J5:J35)</f>
-        <v>40.819999999999993</v>
+        <v>-9.1800000000000068</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="T2" s="3">
         <f xml:space="preserve"> SUM(H2:H34)</f>
-        <v>305.18</v>
+        <v>419.18</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
@@ -3149,13 +3149,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F21" s="9"/>
+      <c r="F21" s="9">
+        <v>50</v>
+      </c>
       <c r="G21" s="1" t="s">
         <v>66</v>
       </c>
       <c r="H21" s="6">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="J21" s="9"/>
     </row>
@@ -3166,16 +3168,18 @@
       <c r="B22" s="3">
         <v>11</v>
       </c>
-      <c r="C22" s="9"/>
+      <c r="C22" s="9">
+        <v>11</v>
+      </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F22" s="9"/>
       <c r="H22" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -3185,16 +3189,18 @@
       <c r="B23" s="3">
         <v>11</v>
       </c>
-      <c r="C23" s="9"/>
+      <c r="C23" s="9">
+        <v>11</v>
+      </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F23" s="9"/>
       <c r="H23" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -3223,16 +3229,18 @@
       <c r="B25" s="3">
         <v>11</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="9">
+        <v>21</v>
+      </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>-10</v>
       </c>
       <c r="F25" s="9"/>
       <c r="H25" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -3242,16 +3250,18 @@
       <c r="B26" s="3">
         <v>11</v>
       </c>
-      <c r="C26" s="9"/>
+      <c r="C26" s="9">
+        <v>11</v>
+      </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F26" s="9"/>
       <c r="H26" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -3261,16 +3271,18 @@
       <c r="B27" s="3">
         <v>11</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="9">
+        <v>10</v>
+      </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F27" s="9"/>
       <c r="H27" s="6">
         <f>SUM(C27,F27)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -5,17 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\网页设计\docs\表账\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478E7998-17DB-4A56-B781-4C7B40B30760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26702EE-02BF-4127-A338-66E6E6752350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
     <sheet name="四月" sheetId="2" r:id="rId2"/>
     <sheet name="五月" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="67">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2677,7 +2679,7 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
@@ -2697,7 +2699,7 @@
       <c r="Q2" s="3"/>
       <c r="T2" s="3">
         <f xml:space="preserve"> SUM(H2:H34)</f>
-        <v>419.18</v>
+        <v>454.18</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
@@ -3292,16 +3294,18 @@
       <c r="B28" s="3">
         <v>11</v>
       </c>
-      <c r="C28" s="9"/>
+      <c r="C28" s="9">
+        <v>11</v>
+      </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F28" s="9"/>
       <c r="H28" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -3311,16 +3315,18 @@
       <c r="B29" s="3">
         <v>11</v>
       </c>
-      <c r="C29" s="9"/>
+      <c r="C29" s="9">
+        <v>13</v>
+      </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>-2</v>
       </c>
       <c r="F29" s="9"/>
       <c r="H29" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
@@ -3330,15 +3336,17 @@
       <c r="B30" s="3">
         <v>11</v>
       </c>
-      <c r="C30" s="9"/>
+      <c r="C30" s="9">
+        <v>11</v>
+      </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F30" s="9"/>
       <c r="H30" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
@@ -3363,9 +3371,12 @@
       <c r="A32" s="2">
         <v>46173</v>
       </c>
+      <c r="B32" s="3">
+        <v>11</v>
+      </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F32" s="9"/>
       <c r="H32" s="6">
@@ -3409,4 +3420,792 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9137FA4-0EB1-474D-A83A-8F989D2F3B19}">
+  <dimension ref="A1:U38"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="30.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="75.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" style="1"/>
+    <col min="20" max="20" width="8.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B2" s="3">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3">
+        <f>B2-C2</f>
+        <v>11</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="H2" s="6">
+        <f>SUM(C2,F2)</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3">
+        <f>AVERAGE(B2:B32)</f>
+        <v>11</v>
+      </c>
+      <c r="K2" s="3">
+        <f>SUM(B2:B31)</f>
+        <v>330</v>
+      </c>
+      <c r="L2" s="3">
+        <f>SUM(C2:C32)</f>
+        <v>37</v>
+      </c>
+      <c r="M2" s="3">
+        <f>SUM(F2:F32)</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="3">
+        <v>200</v>
+      </c>
+      <c r="O2" s="3">
+        <f>SUM(J5:J48)</f>
+        <v>0</v>
+      </c>
+      <c r="P2" s="3">
+        <f>SUM(N2:O2)-M2+SUM(J5:J35)</f>
+        <v>200</v>
+      </c>
+      <c r="Q2" s="3"/>
+      <c r="T2" s="3">
+        <f xml:space="preserve"> SUM(H2:H34)</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B3" s="3">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3">
+        <f t="shared" ref="E3:E33" si="0">B3-C3</f>
+        <v>-1</v>
+      </c>
+      <c r="F3" s="9"/>
+      <c r="H3" s="6">
+        <f t="shared" ref="H3:H34" si="1">SUM(C3,F3)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B4" s="3">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3">
+        <v>13</v>
+      </c>
+      <c r="E4" s="3">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="H4" s="6">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>46177</v>
+      </c>
+      <c r="B5" s="3">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3">
+        <v>12</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="H5" s="6">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="J5" s="9"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B6" s="3">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="E6" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="H6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="9"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B7" s="3">
+        <v>11</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="H7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="9"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>46180</v>
+      </c>
+      <c r="B8" s="3">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="H8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="9"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B9" s="3">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="H9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B10" s="3">
+        <v>11</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="H10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B11" s="3">
+        <v>11</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="H11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="9"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B12" s="3">
+        <v>11</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="E12" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="H12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="9"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B13" s="3">
+        <v>11</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="H13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="9"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B14" s="3">
+        <v>11</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F14" s="9"/>
+      <c r="H14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>46187</v>
+      </c>
+      <c r="B15" s="3">
+        <v>11</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F15" s="9"/>
+      <c r="H15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B16" s="3">
+        <v>11</v>
+      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="H16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B17" s="3">
+        <v>11</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F17" s="9"/>
+      <c r="H17" s="6">
+        <f>SUM(C17,F17)</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B18" s="3">
+        <v>11</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F18" s="9"/>
+      <c r="H18" s="6">
+        <f>SUM(C18,F18)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="9"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B19" s="3">
+        <v>11</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F19" s="9"/>
+      <c r="H19" s="6">
+        <f>SUM(C19,F19)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B20" s="3">
+        <v>11</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F20" s="9"/>
+      <c r="H20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B21" s="3">
+        <v>11</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F21" s="9"/>
+      <c r="H21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="9"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>46194</v>
+      </c>
+      <c r="B22" s="3">
+        <v>11</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F22" s="9"/>
+      <c r="H22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B23" s="3">
+        <v>11</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F23" s="9"/>
+      <c r="H23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B24" s="3">
+        <v>11</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F24" s="9"/>
+      <c r="H24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B25" s="3">
+        <v>11</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F25" s="9"/>
+      <c r="H25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B26" s="3">
+        <v>11</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F26" s="9"/>
+      <c r="H26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B27" s="3">
+        <v>11</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F27" s="9"/>
+      <c r="H27" s="6">
+        <f>SUM(C27,F27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>46200</v>
+      </c>
+      <c r="B28" s="3">
+        <v>11</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F28" s="9"/>
+      <c r="H28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>46201</v>
+      </c>
+      <c r="B29" s="3">
+        <v>11</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F29" s="9"/>
+      <c r="H29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B30" s="3">
+        <v>11</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="E30" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="H30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>46203</v>
+      </c>
+      <c r="B31" s="3">
+        <v>11</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="E31" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="H31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B32" s="3">
+        <v>11</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F32" s="9"/>
+      <c r="H32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>46205</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="9"/>
+      <c r="H33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="2"/>
+      <c r="F34" s="9"/>
+      <c r="H34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="2"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="2"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="2"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB7B261D-676A-4238-BFE3-629FB440D984}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26702EE-02BF-4127-A338-66E6E6752350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B9E697-7198-4D0D-B6FD-DE83B6F37E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="68">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -310,6 +310,10 @@
   </si>
   <si>
     <t>网易云会员 50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 数位屏 xppen artist 12 679 （预期折价100，两年，目前二手市场均价800）实行租用计算方法</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -322,7 +326,7 @@
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="177" formatCode="_ [$¥-804]* #,##0.00_ ;_ [$¥-804]* \-#,##0.00_ ;_ [$¥-804]* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,8 +356,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -363,6 +375,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -375,7 +392,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -383,8 +400,11 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -408,11 +428,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="差" xfId="1" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="适中" xfId="3" builtinId="28"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -3537,14 +3561,14 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>37</v>
+        <v>93.17</v>
       </c>
       <c r="M2" s="3">
         <f>SUM(F2:F32)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N2" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O2" s="3">
         <f>SUM(J5:J48)</f>
@@ -3557,7 +3581,7 @@
       <c r="Q2" s="3"/>
       <c r="T2" s="3">
         <f xml:space="preserve"> SUM(H2:H34)</f>
-        <v>37</v>
+        <v>193.17</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
@@ -3644,15 +3668,17 @@
       <c r="B6" s="3">
         <v>11</v>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3">
+        <v>10</v>
+      </c>
       <c r="E6" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F6" s="9"/>
       <c r="H6" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J6" s="9"/>
     </row>
@@ -3663,16 +3689,23 @@
       <c r="B7" s="3">
         <v>11</v>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3">
+        <v>11.38</v>
+      </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="F7" s="9"/>
+        <v>-0.38000000000000078</v>
+      </c>
+      <c r="F7" s="9">
+        <v>100</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>67</v>
+      </c>
       <c r="H7" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>111.38</v>
       </c>
       <c r="J7" s="9"/>
     </row>
@@ -3683,16 +3716,18 @@
       <c r="B8" s="3">
         <v>11</v>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3">
+        <v>9.7899999999999991</v>
+      </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1.2100000000000009</v>
       </c>
       <c r="F8" s="9"/>
       <c r="H8" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="J8" s="9"/>
     </row>
@@ -3703,16 +3738,18 @@
       <c r="B9" s="3">
         <v>11</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3">
+        <v>13</v>
+      </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>-2</v>
       </c>
       <c r="F9" s="9"/>
       <c r="H9" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J9" s="9"/>
     </row>
@@ -3723,16 +3760,18 @@
       <c r="B10" s="3">
         <v>11</v>
       </c>
-      <c r="C10" s="9"/>
+      <c r="C10" s="9">
+        <v>12</v>
+      </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="F10" s="9"/>
       <c r="H10" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J10" s="9"/>
     </row>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B9E697-7198-4D0D-B6FD-DE83B6F37E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF107B2-CCBA-4AC8-BCF7-512ECCC5C8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="76">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -314,6 +314,38 @@
   </si>
   <si>
     <t xml:space="preserve"> 数位屏 xppen artist 12 679 （预期折价100，两年，目前二手市场均价800）实行租用计算方法</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>esim实体卡 20+电话卡充值 91</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐用品展期（beta)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>内容</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>外国手机卡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>平摊成本</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数位屏（租用计价）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>预期时间（信用)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -321,10 +353,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;¥&quot;* #,##0.00_ ;_ &quot;¥&quot;* \-#,##0.00_ ;_ &quot;¥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="177" formatCode="_ [$¥-804]* #,##0.00_ ;_ [$¥-804]* \-#,##0.00_ ;_ [$¥-804]* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -404,7 +437,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -429,6 +462,12 @@
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3459,9 +3498,10 @@
     <col min="7" max="7" width="75.125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.125" style="5" customWidth="1"/>
     <col min="9" max="9" width="7.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.25" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13" style="1" customWidth="1"/>
@@ -3556,16 +3596,16 @@
         <v>11</v>
       </c>
       <c r="K2" s="3">
-        <f>SUM(B2:B31)</f>
+        <f>SUM(B2:B36)</f>
         <v>330</v>
       </c>
       <c r="L2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>93.17</v>
+        <v>103.17</v>
       </c>
       <c r="M2" s="3">
-        <f>SUM(F2:F32)</f>
-        <v>100</v>
+        <f>SUM(F2:F32)+SUM(M14:M15)-SUM(K14:K16)</f>
+        <v>17.583333333333343</v>
       </c>
       <c r="N2" s="3">
         <v>300</v>
@@ -3576,12 +3616,12 @@
       </c>
       <c r="P2" s="3">
         <f>SUM(N2:O2)-M2+SUM(J5:J35)</f>
-        <v>200</v>
+        <v>282.41666666666663</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="T2" s="3">
         <f xml:space="preserve"> SUM(H2:H34)</f>
-        <v>193.17</v>
+        <v>314.16999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
@@ -3782,16 +3822,23 @@
       <c r="B11" s="3">
         <v>11</v>
       </c>
-      <c r="C11" s="9"/>
+      <c r="C11" s="9">
+        <v>10</v>
+      </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="F11" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="F11" s="9">
+        <v>111</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="H11" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="J11" s="9"/>
     </row>
@@ -3812,7 +3859,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J12" s="9"/>
+      <c r="J12" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
@@ -3832,7 +3883,18 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J13" s="9"/>
+      <c r="J13" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
@@ -3852,7 +3914,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J14" s="9"/>
+      <c r="J14" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="K14" s="13">
+        <v>111</v>
+      </c>
+      <c r="L14" s="13">
+        <v>12</v>
+      </c>
+      <c r="M14" s="13">
+        <f>K14/L14</f>
+        <v>9.25</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
@@ -3872,7 +3946,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="9"/>
+      <c r="J15" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="K15" s="13">
+        <v>100</v>
+      </c>
+      <c r="L15" s="13">
+        <v>12</v>
+      </c>
+      <c r="M15" s="13">
+        <f>K15/L15</f>
+        <v>8.3333333333333339</v>
+      </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
@@ -3893,8 +3979,11 @@
         <v>0</v>
       </c>
       <c r="J16" s="9"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>46189</v>
       </c>
@@ -3913,8 +4002,11 @@
         <v>0</v>
       </c>
       <c r="J17" s="9"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>46190</v>
       </c>
@@ -3933,8 +4025,11 @@
         <v>0</v>
       </c>
       <c r="J18" s="9"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>46191</v>
       </c>
@@ -3954,7 +4049,7 @@
       </c>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>46192</v>
       </c>
@@ -3974,7 +4069,7 @@
       </c>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>46193</v>
       </c>
@@ -3994,7 +4089,7 @@
       </c>
       <c r="J21" s="9"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>46194</v>
       </c>
@@ -4013,7 +4108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>46195</v>
       </c>
@@ -4032,7 +4127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>46196</v>
       </c>
@@ -4051,7 +4146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>46197</v>
       </c>
@@ -4070,7 +4165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>46198</v>
       </c>
@@ -4089,7 +4184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>46199</v>
       </c>
@@ -4108,7 +4203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>46200</v>
       </c>
@@ -4127,7 +4222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>46201</v>
       </c>
@@ -4146,7 +4241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>46202</v>
       </c>
@@ -4164,7 +4259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>46203</v>
       </c>
@@ -4182,44 +4277,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" s="2">
-        <v>46204</v>
-      </c>
-      <c r="B32" s="3">
-        <v>11</v>
-      </c>
-      <c r="E32" s="3">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3"/>
+      <c r="E32" s="3"/>
       <c r="F32" s="9"/>
-      <c r="H32" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="2">
-        <v>46205</v>
-      </c>
-      <c r="E33" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A33" s="2"/>
+      <c r="E33" s="3"/>
       <c r="F33" s="9"/>
-      <c r="H33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="F34" s="9"/>
-      <c r="H34" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
@@ -4234,6 +4308,9 @@
       <c r="A38" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="J12:L12"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF107B2-CCBA-4AC8-BCF7-512ECCC5C8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F5393B-52A4-4366-BBE1-6FDE84E8C711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="三月" sheetId="1" r:id="rId1"/>
     <sheet name="四月" sheetId="2" r:id="rId2"/>
     <sheet name="五月" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="5" r:id="rId4"/>
+    <sheet name="六月" sheetId="5" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="89">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -313,18 +313,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 数位屏 xppen artist 12 679 （预期折价100，两年，目前二手市场均价800）实行租用计算方法</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>esim实体卡 20+电话卡充值 91</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>耐用品展期（beta)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>内容</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -337,15 +325,79 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>平摊成本</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>数位屏（租用计价）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>预期时间（信用)</t>
+    <t>预期信用时间（月）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐用品展期公示（beta)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>账目开销</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>esim实体卡 20+电话卡充值 91(平摊计价）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 数位屏 xppen artist 12 679 （预期折价100，1年，目前二手市场均价800）实行租用计算方法</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>平摊</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>结束时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>外卖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>购置网页框架（含学习补助）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>已补助</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>购置codex会员 80</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>购置网页框架（含学习补助）105</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>学习补助</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>比例（不安定变动）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>学习补助（出于学习目的的补助）（beta)（10%-100%）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过去时候给别人当牛马时候想到的说辞。即：是为我目前做的事情提供学习补助，如果含有学习的目的即可提供补助，让我重新审视我做的事情。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有579元未纳入计算因为实行租用计算方法</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -416,12 +468,92 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -437,7 +569,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -467,8 +599,62 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3487,7 +3673,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9137FA4-0EB1-474D-A83A-8F989D2F3B19}">
-  <dimension ref="A1:U38"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.625" style="1" bestFit="1" customWidth="1"/>
@@ -3496,24 +3682,21 @@
     <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
     <col min="7" max="7" width="75.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="7.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13" style="1" customWidth="1"/>
-    <col min="17" max="17" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9" style="1"/>
-    <col min="20" max="20" width="8.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9" style="1"/>
+    <col min="8" max="8" width="8.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="39.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9" style="1"/>
+    <col min="18" max="18" width="8.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3536,43 +3719,37 @@
         <v>5</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>6</v>
+        <v>73</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>46174</v>
       </c>
@@ -3590,41 +3767,38 @@
         <f>SUM(C2,F2)</f>
         <v>0</v>
       </c>
-      <c r="I2" s="3"/>
+      <c r="I2" s="3">
+        <f>AVERAGE(B2:B32)</f>
+        <v>11</v>
+      </c>
       <c r="J2" s="3">
-        <f>AVERAGE(B2:B32)</f>
-        <v>11</v>
-      </c>
-      <c r="K2" s="3">
         <f>SUM(B2:B36)</f>
         <v>330</v>
       </c>
+      <c r="K2" s="3">
+        <f>SUM(C2:C32)</f>
+        <v>150.17000000000002</v>
+      </c>
       <c r="L2" s="3">
-        <f>SUM(C2:C32)</f>
-        <v>103.17</v>
+        <f>SUM(F2:F32)+SUM(M14:M15)-SUM(J14:J16)</f>
+        <v>202.58333333333331</v>
       </c>
       <c r="M2" s="3">
-        <f>SUM(F2:F32)+SUM(M14:M15)-SUM(K14:K16)</f>
-        <v>17.583333333333343</v>
+        <v>300</v>
       </c>
       <c r="N2" s="3">
-        <v>300</v>
+        <f>SUM(I5:I48)</f>
+        <v>0</v>
       </c>
       <c r="O2" s="3">
-        <f>SUM(J5:J48)</f>
-        <v>0</v>
-      </c>
-      <c r="P2" s="3">
-        <f>SUM(N2:O2)-M2+SUM(J5:J35)</f>
-        <v>282.41666666666663</v>
-      </c>
-      <c r="Q2" s="3"/>
-      <c r="T2" s="3">
-        <f xml:space="preserve"> SUM(H2:H34)</f>
-        <v>314.16999999999996</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+        <f>SUM(M2:N2)-L2</f>
+        <v>97.416666666666686</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>46175</v>
       </c>
@@ -3636,16 +3810,16 @@
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E33" si="0">B3-C3</f>
+        <f t="shared" ref="E3:E31" si="0">B3-C3</f>
         <v>-1</v>
       </c>
       <c r="F3" s="9"/>
       <c r="H3" s="6">
-        <f t="shared" ref="H3:H34" si="1">SUM(C3,F3)</f>
+        <f t="shared" ref="H3:H31" si="1">SUM(C3,F3)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46176</v>
       </c>
@@ -3664,23 +3838,29 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="J4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>46177</v>
       </c>
@@ -3699,9 +3879,17 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="J5" s="9"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="I5" s="9"/>
+      <c r="N5" s="3">
+        <f xml:space="preserve"> K2+L2</f>
+        <v>352.75333333333333</v>
+      </c>
+      <c r="O5" s="12">
+        <f>SUM(M26:M33)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>46178</v>
       </c>
@@ -3720,9 +3908,9 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J6" s="9"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="I6" s="9"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46179</v>
       </c>
@@ -3741,15 +3929,15 @@
         <v>100</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H7" s="6">
         <f t="shared" si="1"/>
         <v>111.38</v>
       </c>
-      <c r="J7" s="9"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>46180</v>
       </c>
@@ -3769,9 +3957,9 @@
         <f t="shared" si="1"/>
         <v>9.7899999999999991</v>
       </c>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="I8" s="9"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>46181</v>
       </c>
@@ -3791,9 +3979,9 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>46182</v>
       </c>
@@ -3813,9 +4001,9 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="I10" s="9"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>46183</v>
       </c>
@@ -3833,134 +4021,167 @@
       <c r="F11" s="9">
         <v>111</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>68</v>
+      <c r="G11" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="H11" s="6">
         <f t="shared" si="1"/>
         <v>121</v>
       </c>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>46184</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
       </c>
-      <c r="C12" s="9"/>
+      <c r="C12" s="9">
+        <v>11</v>
+      </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F12" s="9"/>
       <c r="H12" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="28"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>46185</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
       </c>
-      <c r="C13" s="9"/>
+      <c r="C13" s="9">
+        <v>12</v>
+      </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="F13" s="9"/>
+        <v>-1</v>
+      </c>
+      <c r="F13" s="9">
+        <v>80</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="H13" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="K13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="K13" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="L13" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>46186</v>
       </c>
       <c r="B14" s="3">
         <v>11</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="3"/>
+      <c r="C14" s="9">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="F14" s="9"/>
+        <v>-2</v>
+      </c>
+      <c r="F14" s="9">
+        <v>105</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="H14" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="K14" s="13">
+        <v>118</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="J14" s="20">
         <v>111</v>
       </c>
-      <c r="L14" s="13">
+      <c r="K14" s="18">
         <v>12</v>
       </c>
-      <c r="M14" s="13">
-        <f>K14/L14</f>
+      <c r="L14" s="29">
+        <v>46539</v>
+      </c>
+      <c r="M14" s="22">
+        <f>J14/K14</f>
         <v>9.25</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>46187</v>
       </c>
       <c r="B15" s="3">
         <v>11</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="3"/>
+      <c r="C15" s="9">
+        <v>11</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F15" s="9"/>
       <c r="H15" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="K15" s="13">
+        <v>11</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="J15" s="20">
         <v>100</v>
       </c>
-      <c r="L15" s="13">
+      <c r="K15" s="18">
         <v>12</v>
       </c>
-      <c r="M15" s="13">
-        <f>K15/L15</f>
+      <c r="L15" s="29">
+        <v>46539</v>
+      </c>
+      <c r="M15" s="22">
+        <f>J15/K15</f>
         <v>8.3333333333333339</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>46188</v>
       </c>
@@ -3978,12 +4199,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J16" s="9"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I16" s="16"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="22"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>46189</v>
       </c>
@@ -4001,12 +4223,13 @@
         <f>SUM(C17,F17)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="9"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I17" s="24"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="23"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>46190</v>
       </c>
@@ -4024,12 +4247,13 @@
         <f>SUM(C18,F18)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="9"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I18" s="24"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="23"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>46191</v>
       </c>
@@ -4047,9 +4271,13 @@
         <f>SUM(C19,F19)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="9"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I19" s="24"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="23"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>46192</v>
       </c>
@@ -4067,9 +4295,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="9"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I20" s="25"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="27"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>46193</v>
       </c>
@@ -4087,9 +4319,8 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="9"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>46194</v>
       </c>
@@ -4108,7 +4339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>46195</v>
       </c>
@@ -4127,7 +4358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>46196</v>
       </c>
@@ -4145,8 +4376,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I24" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="O24" s="31"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>46197</v>
       </c>
@@ -4164,8 +4406,25 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I25" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="L25" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="M25" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="N25" s="30"/>
+      <c r="O25" s="31"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>46198</v>
       </c>
@@ -4183,8 +4442,27 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I26" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="J26" s="20">
+        <v>105</v>
+      </c>
+      <c r="K26" s="21">
+        <v>0.4</v>
+      </c>
+      <c r="L26" s="20">
+        <f>J26*(1-K26)</f>
+        <v>63</v>
+      </c>
+      <c r="M26" s="22">
+        <f>J26-L26</f>
+        <v>42</v>
+      </c>
+      <c r="N26" s="30"/>
+      <c r="O26" s="31"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>46199</v>
       </c>
@@ -4202,8 +4480,15 @@
         <f>SUM(C27,F27)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I27" s="16"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="31"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>46200</v>
       </c>
@@ -4221,8 +4506,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I28" s="16"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="31"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>46201</v>
       </c>
@@ -4240,8 +4532,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I29" s="24"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="31"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>46202</v>
       </c>
@@ -4258,8 +4557,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I30" s="24"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="23"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="31"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>46203</v>
       </c>
@@ -4276,27 +4582,47 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I31" s="24"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="31"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="9"/>
       <c r="H32" s="6"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="27"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="31"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="E33" s="3"/>
       <c r="F33" s="9"/>
-      <c r="H33" s="6"/>
+      <c r="H33" s="5" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="F34" s="9"/>
-      <c r="H34" s="6"/>
+      <c r="H34" s="6">
+        <f>SUM(H2:H32)</f>
+        <v>546.16999999999996</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
+      <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
@@ -4308,8 +4634,10 @@
       <c r="A38" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="J12:L12"/>
+  <mergeCells count="3">
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="N24:O32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F5393B-52A4-4366-BBE1-6FDE84E8C711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B80E45F-3AD7-4E55-BD02-1F28297CD671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -398,6 +398,18 @@
   </si>
   <si>
     <t>有579元未纳入计算因为实行租用计算方法</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">一菜一肉8.8 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5kg的面包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>头孢以及雷氯他定</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -599,12 +611,6 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -648,6 +654,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3769,19 +3781,19 @@
       </c>
       <c r="I2" s="3">
         <f>AVERAGE(B2:B32)</f>
-        <v>11</v>
+        <v>11.906666666666668</v>
       </c>
       <c r="J2" s="3">
         <f>SUM(B2:B36)</f>
-        <v>330</v>
+        <v>357.20000000000005</v>
       </c>
       <c r="K2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>150.17000000000002</v>
+        <v>278.77000000000004</v>
       </c>
       <c r="L2" s="3">
         <f>SUM(F2:F32)+SUM(M14:M15)-SUM(J14:J16)</f>
-        <v>202.58333333333331</v>
+        <v>264.88333333333333</v>
       </c>
       <c r="M2" s="3">
         <v>300</v>
@@ -3792,7 +3804,7 @@
       </c>
       <c r="O2" s="3">
         <f>SUM(M2:N2)-L2</f>
-        <v>97.416666666666686</v>
+        <v>35.116666666666674</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>88</v>
@@ -3882,11 +3894,11 @@
       <c r="I5" s="9"/>
       <c r="N5" s="3">
         <f xml:space="preserve"> K2+L2</f>
-        <v>352.75333333333333</v>
+        <v>543.65333333333342</v>
       </c>
       <c r="O5" s="12">
         <f>SUM(M26:M33)</f>
-        <v>42</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
@@ -4049,13 +4061,13 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="28"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="26"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
@@ -4082,19 +4094,19 @@
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="J13" s="17" t="s">
+      <c r="J13" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="K13" s="17" t="s">
+      <c r="K13" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="L13" s="17" t="s">
+      <c r="L13" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="M13" s="23" t="s">
+      <c r="M13" s="21" t="s">
         <v>77</v>
       </c>
     </row>
@@ -4125,19 +4137,19 @@
         <f t="shared" si="1"/>
         <v>118</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J14" s="18">
         <v>111</v>
       </c>
-      <c r="K14" s="18">
+      <c r="K14" s="16">
         <v>12</v>
       </c>
-      <c r="L14" s="29">
+      <c r="L14" s="27">
         <v>46539</v>
       </c>
-      <c r="M14" s="22">
+      <c r="M14" s="20">
         <f>J14/K14</f>
         <v>9.25</v>
       </c>
@@ -4164,19 +4176,19 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="18">
         <v>100</v>
       </c>
-      <c r="K15" s="18">
+      <c r="K15" s="16">
         <v>12</v>
       </c>
-      <c r="L15" s="29">
+      <c r="L15" s="27">
         <v>46539</v>
       </c>
-      <c r="M15" s="22">
+      <c r="M15" s="20">
         <f>J15/K15</f>
         <v>8.3333333333333339</v>
       </c>
@@ -4188,22 +4200,24 @@
       <c r="B16" s="3">
         <v>11</v>
       </c>
-      <c r="C16" s="9"/>
+      <c r="C16" s="9">
+        <v>10</v>
+      </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F16" s="9"/>
       <c r="H16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="16"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="22"/>
+        <v>10</v>
+      </c>
+      <c r="I16" s="14"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="20"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
@@ -4212,22 +4226,24 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="9"/>
+      <c r="C17" s="12">
+        <v>10</v>
+      </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F17" s="9"/>
       <c r="H17" s="6">
         <f>SUM(C17,F17)</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="24"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="23"/>
+        <v>10</v>
+      </c>
+      <c r="I17" s="22"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="21"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
@@ -4236,22 +4252,24 @@
       <c r="B18" s="3">
         <v>11</v>
       </c>
-      <c r="C18" s="9"/>
+      <c r="C18" s="12">
+        <v>10</v>
+      </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F18" s="9"/>
       <c r="H18" s="6">
         <f>SUM(C18,F18)</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="24"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="23"/>
+        <v>10</v>
+      </c>
+      <c r="I18" s="22"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="21"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
@@ -4260,22 +4278,24 @@
       <c r="B19" s="3">
         <v>11</v>
       </c>
-      <c r="C19" s="9"/>
+      <c r="C19" s="12">
+        <v>10</v>
+      </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F19" s="9"/>
       <c r="H19" s="6">
         <f>SUM(C19,F19)</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="24"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="23"/>
+        <v>10</v>
+      </c>
+      <c r="I19" s="22"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="21"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
@@ -4284,7 +4304,9 @@
       <c r="B20" s="3">
         <v>11</v>
       </c>
-      <c r="C20" s="9"/>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
@@ -4295,11 +4317,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="25"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="26"/>
-      <c r="M20" s="27"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="25"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
@@ -4308,16 +4330,18 @@
       <c r="B21" s="3">
         <v>11</v>
       </c>
-      <c r="C21" s="9"/>
+      <c r="C21" s="9">
+        <v>12</v>
+      </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="F21" s="9"/>
       <c r="H21" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
@@ -4327,16 +4351,20 @@
       <c r="B22" s="3">
         <v>11</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="3"/>
+      <c r="C22" s="9">
+        <v>20</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>-9</v>
       </c>
       <c r="F22" s="9"/>
       <c r="H22" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
@@ -4346,7 +4374,9 @@
       <c r="B23" s="3">
         <v>11</v>
       </c>
-      <c r="C23" s="9"/>
+      <c r="C23" s="9">
+        <v>0</v>
+      </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
@@ -4365,7 +4395,9 @@
       <c r="B24" s="3">
         <v>11</v>
       </c>
-      <c r="C24" s="9"/>
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3">
         <f t="shared" si="0"/>
@@ -4376,13 +4408,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="I24" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="15"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="13"/>
       <c r="N24" s="30" t="s">
         <v>87</v>
       </c>
@@ -4395,30 +4427,37 @@
       <c r="B25" s="3">
         <v>11</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="9">
+        <v>12</v>
+      </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="F25" s="9"/>
+        <v>-1</v>
+      </c>
+      <c r="F25" s="9">
+        <v>62.3</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="H25" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="16" t="s">
+        <v>74.3</v>
+      </c>
+      <c r="I25" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="J25" s="17" t="s">
+      <c r="J25" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="K25" s="18" t="s">
+      <c r="K25" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="L25" s="18" t="s">
+      <c r="L25" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="M25" s="19" t="s">
+      <c r="M25" s="17" t="s">
         <v>81</v>
       </c>
       <c r="N25" s="30"/>
@@ -4431,33 +4470,35 @@
       <c r="B26" s="3">
         <v>11</v>
       </c>
-      <c r="C26" s="9"/>
+      <c r="C26" s="9">
+        <v>13</v>
+      </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>-2</v>
       </c>
       <c r="F26" s="9"/>
       <c r="H26" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="J26" s="20">
+      <c r="J26" s="18">
         <v>105</v>
       </c>
-      <c r="K26" s="21">
-        <v>0.4</v>
-      </c>
-      <c r="L26" s="20">
+      <c r="K26" s="19">
+        <v>0.1</v>
+      </c>
+      <c r="L26" s="18">
         <f>J26*(1-K26)</f>
-        <v>63</v>
-      </c>
-      <c r="M26" s="22">
+        <v>94.5</v>
+      </c>
+      <c r="M26" s="20">
         <f>J26-L26</f>
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="N26" s="30"/>
       <c r="O26" s="31"/>
@@ -4469,22 +4510,26 @@
       <c r="B27" s="3">
         <v>11</v>
       </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="3"/>
+      <c r="C27" s="9">
+        <v>13.8</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>-2.8000000000000007</v>
       </c>
       <c r="F27" s="9"/>
       <c r="H27" s="6">
         <f>SUM(C27,F27)</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="16"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="23"/>
+        <v>13.8</v>
+      </c>
+      <c r="I27" s="14"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="21"/>
       <c r="N27" s="30"/>
       <c r="O27" s="31"/>
     </row>
@@ -4492,25 +4537,27 @@
       <c r="A28" s="2">
         <v>46200</v>
       </c>
-      <c r="B28" s="3">
-        <v>11</v>
-      </c>
-      <c r="C28" s="9"/>
+      <c r="B28" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C28" s="12">
+        <v>17.8</v>
+      </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F28" s="9"/>
       <c r="H28" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="16"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="23"/>
+        <v>17.8</v>
+      </c>
+      <c r="I28" s="14"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="21"/>
       <c r="N28" s="30"/>
       <c r="O28" s="31"/>
     </row>
@@ -4518,25 +4565,25 @@
       <c r="A29" s="2">
         <v>46201</v>
       </c>
-      <c r="B29" s="3">
-        <v>11</v>
+      <c r="B29" s="12">
+        <v>17.8</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>17.8</v>
       </c>
       <c r="F29" s="9"/>
       <c r="H29" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I29" s="24"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="23"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="21"/>
       <c r="N29" s="30"/>
       <c r="O29" s="31"/>
     </row>
@@ -4544,24 +4591,24 @@
       <c r="A30" s="2">
         <v>46202</v>
       </c>
-      <c r="B30" s="3">
-        <v>11</v>
+      <c r="B30" s="12">
+        <v>17.8</v>
       </c>
       <c r="C30" s="9"/>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>17.8</v>
       </c>
       <c r="F30" s="9"/>
       <c r="H30" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I30" s="24"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="23"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="21"/>
       <c r="N30" s="30"/>
       <c r="O30" s="31"/>
     </row>
@@ -4569,24 +4616,24 @@
       <c r="A31" s="2">
         <v>46203</v>
       </c>
-      <c r="B31" s="3">
-        <v>11</v>
+      <c r="B31" s="12">
+        <v>17.8</v>
       </c>
       <c r="C31" s="9"/>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>17.8</v>
       </c>
       <c r="F31" s="9"/>
       <c r="H31" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I31" s="24"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="23"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="21"/>
       <c r="N31" s="30"/>
       <c r="O31" s="31"/>
     </row>
@@ -4596,11 +4643,11 @@
       <c r="E32" s="3"/>
       <c r="F32" s="9"/>
       <c r="H32" s="6"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="27"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="25"/>
       <c r="N32" s="30"/>
       <c r="O32" s="31"/>
     </row>
@@ -4617,7 +4664,7 @@
       <c r="F34" s="9"/>
       <c r="H34" s="6">
         <f>SUM(H2:H32)</f>
-        <v>546.16999999999996</v>
+        <v>737.06999999999982</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B80E45F-3AD7-4E55-BD02-1F28297CD671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7006E5B-8E5D-4FD9-87BF-EBEFAFB67FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="三月" sheetId="1" r:id="rId1"/>
     <sheet name="四月" sheetId="2" r:id="rId2"/>
     <sheet name="五月" sheetId="3" r:id="rId3"/>
     <sheet name="六月" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId5"/>
+    <sheet name="七月" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="K2" s="3">
         <f>SUM(C2:C32)</f>
-        <v>278.77000000000004</v>
+        <v>332.17000000000007</v>
       </c>
       <c r="L2" s="3">
         <f>SUM(F2:F32)+SUM(M14:M15)-SUM(J14:J16)</f>
@@ -3894,7 +3894,7 @@
       <c r="I5" s="9"/>
       <c r="N5" s="3">
         <f xml:space="preserve"> K2+L2</f>
-        <v>543.65333333333342</v>
+        <v>597.0533333333334</v>
       </c>
       <c r="O5" s="12">
         <f>SUM(M26:M33)</f>
@@ -4568,16 +4568,18 @@
       <c r="B29" s="12">
         <v>17.8</v>
       </c>
-      <c r="C29" s="9"/>
+      <c r="C29" s="12">
+        <v>17.8</v>
+      </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>17.8</v>
+        <v>0</v>
       </c>
       <c r="F29" s="9"/>
       <c r="H29" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="I29" s="22"/>
       <c r="J29" s="15"/>
@@ -4594,15 +4596,17 @@
       <c r="B30" s="12">
         <v>17.8</v>
       </c>
-      <c r="C30" s="9"/>
+      <c r="C30" s="12">
+        <v>17.8</v>
+      </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>17.8</v>
+        <v>0</v>
       </c>
       <c r="F30" s="9"/>
       <c r="H30" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="I30" s="22"/>
       <c r="J30" s="15"/>
@@ -4619,15 +4623,17 @@
       <c r="B31" s="12">
         <v>17.8</v>
       </c>
-      <c r="C31" s="9"/>
+      <c r="C31" s="12">
+        <v>17.8</v>
+      </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>17.8</v>
+        <v>0</v>
       </c>
       <c r="F31" s="9"/>
       <c r="H31" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="I31" s="22"/>
       <c r="J31" s="15"/>
@@ -4664,7 +4670,7 @@
       <c r="F34" s="9"/>
       <c r="H34" s="6">
         <f>SUM(H2:H32)</f>
-        <v>737.06999999999982</v>
+        <v>790.46999999999969</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -4693,9 +4699,1124 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB7B261D-676A-4238-BFE3-629FB440D984}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="39.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B2" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C2" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3">
+        <f>B2-C2</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="6">
+        <f>SUM(C2,F2)</f>
+        <v>17.8</v>
+      </c>
+      <c r="I2" s="3">
+        <f>AVERAGE(B2:B32)</f>
+        <v>17.800000000000004</v>
+      </c>
+      <c r="J2" s="3">
+        <f>SUM(B2:B36)</f>
+        <v>534.00000000000011</v>
+      </c>
+      <c r="K2" s="3">
+        <f>SUM(C2:C32)</f>
+        <v>35.6</v>
+      </c>
+      <c r="L2" s="3">
+        <f>SUM(F2:F32)+SUM(M14:M15)-SUM(J14:J16)</f>
+        <v>-193.41666666666666</v>
+      </c>
+      <c r="M2" s="3">
+        <v>300</v>
+      </c>
+      <c r="N2" s="3">
+        <f>SUM(I5:I48)</f>
+        <v>0</v>
+      </c>
+      <c r="O2" s="3">
+        <f>SUM(M2:N2)-L2</f>
+        <v>493.41666666666663</v>
+      </c>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>46205</v>
+      </c>
+      <c r="B3" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C3" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3">
+        <f t="shared" ref="E3:E31" si="0">B3-C3</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="12"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="6">
+        <f t="shared" ref="H3:H31" si="1">SUM(C3,F3)</f>
+        <v>17.8</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>46206</v>
+      </c>
+      <c r="B4" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>46207</v>
+      </c>
+      <c r="B5" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="12"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="3">
+        <f xml:space="preserve"> K2+L2</f>
+        <v>-157.81666666666666</v>
+      </c>
+      <c r="O5" s="12">
+        <f>SUM(M26:M33)</f>
+        <v>10.5</v>
+      </c>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>46208</v>
+      </c>
+      <c r="B6" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="12"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>46209</v>
+      </c>
+      <c r="B7" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="12"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>46210</v>
+      </c>
+      <c r="B8" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="12"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>46211</v>
+      </c>
+      <c r="B9" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F9" s="12"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="12"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>46212</v>
+      </c>
+      <c r="B10" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="12"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>46213</v>
+      </c>
+      <c r="B11" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="12"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>46214</v>
+      </c>
+      <c r="B12" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>46215</v>
+      </c>
+      <c r="B13" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B14" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="J14" s="18">
+        <v>111</v>
+      </c>
+      <c r="K14" s="16">
+        <v>12</v>
+      </c>
+      <c r="L14" s="27">
+        <v>46539</v>
+      </c>
+      <c r="M14" s="20">
+        <f>J14/K14</f>
+        <v>9.25</v>
+      </c>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B15" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F15" s="12"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J15" s="18">
+        <v>100</v>
+      </c>
+      <c r="K15" s="16">
+        <v>12</v>
+      </c>
+      <c r="L15" s="27">
+        <v>46539</v>
+      </c>
+      <c r="M15" s="20">
+        <f>J15/K15</f>
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B16" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F16" s="12"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="14"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B17" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="6">
+        <f>SUM(C17,F17)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="22"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>46220</v>
+      </c>
+      <c r="B18" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="6">
+        <f>SUM(C18,F18)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="22"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B19" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F19" s="12"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="6">
+        <f>SUM(C19,F19)</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="22"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>46222</v>
+      </c>
+      <c r="B20" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F20" s="12"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="23"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B21" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>46224</v>
+      </c>
+      <c r="B22" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F22" s="12"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>46225</v>
+      </c>
+      <c r="B23" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F23" s="12"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B24" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C24" s="12"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F24" s="12"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="O24" s="31"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B25" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M25" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N25" s="30"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>46228</v>
+      </c>
+      <c r="B26" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C26" s="12"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F26" s="12"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="J26" s="18">
+        <v>105</v>
+      </c>
+      <c r="K26" s="19">
+        <v>0.1</v>
+      </c>
+      <c r="L26" s="18">
+        <f>J26*(1-K26)</f>
+        <v>94.5</v>
+      </c>
+      <c r="M26" s="20">
+        <f>J26-L26</f>
+        <v>10.5</v>
+      </c>
+      <c r="N26" s="30"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>46229</v>
+      </c>
+      <c r="B27" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C27" s="12"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F27" s="12"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="6">
+        <f>SUM(C27,F27)</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="14"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="31"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B28" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F28" s="12"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="14"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>46231</v>
+      </c>
+      <c r="B29" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C29" s="12"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F29" s="12"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="22"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>46232</v>
+      </c>
+      <c r="B30" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F30" s="12"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="22"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>46233</v>
+      </c>
+      <c r="B31" s="12">
+        <v>17.8</v>
+      </c>
+      <c r="C31" s="12"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="3">
+        <f t="shared" si="0"/>
+        <v>17.8</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="22"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A33" s="2"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A34" s="2"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="6">
+        <f>SUM(H2:H32)</f>
+        <v>35.6</v>
+      </c>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="N24:O32"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/表账/2026/2026预算收支报表.xlsx
+++ b/docs/表账/2026/2026预算收支报表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\网页设计\docs\表账\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7006E5B-8E5D-4FD9-87BF-EBEFAFB67FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39016EF-B064-49AD-A171-3FDD3E8CA037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="99">
   <si>
     <t>时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -410,6 +410,34 @@
   </si>
   <si>
     <t>头孢以及雷氯他定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>回家的车费 44 +高速费用9 +感谢费（小费）10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>牙套400（原价100）+往返车费30 + 共享单车 3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏购置（squad）58</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机会开支补偿</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>补偿源头</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>照顾小孩赚的300</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏购置（）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -581,7 +609,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -667,6 +695,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3676,6 +3707,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
+      <c r="H38" s="6">
+        <f>SUM(H2:H34)</f>
+        <v>454.18</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4704,7 +4739,7 @@
   <cols>
     <col min="1" max="1" width="14.625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.25" bestFit="1" customWidth="1"/>
@@ -4802,10 +4837,11 @@
       </c>
       <c r="L2" s="3">
         <f>SUM(F2:F32)+SUM(M14:M15)-SUM(J14:J16)</f>
-        <v>-193.41666666666666</v>
+        <v>468.58333333333337</v>
       </c>
       <c r="M2" s="3">
-        <v>300</v>
+        <f>300+300</f>
+        <v>600</v>
       </c>
       <c r="N2" s="3">
         <f>SUM(I5:I48)</f>
@@ -4813,7 +4849,7 @@
       </c>
       <c r="O2" s="3">
         <f>SUM(M2:N2)-L2</f>
-        <v>493.41666666666663</v>
+        <v>131.41666666666663</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
@@ -4922,7 +4958,7 @@
       <c r="M5" s="1"/>
       <c r="N5" s="3">
         <f xml:space="preserve"> K2+L2</f>
-        <v>-157.81666666666666</v>
+        <v>504.18333333333339</v>
       </c>
       <c r="O5" s="12">
         <f>SUM(M26:M33)</f>
@@ -4975,19 +5011,27 @@
         <f t="shared" si="0"/>
         <v>17.8</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="11"/>
+      <c r="F7" s="12">
+        <v>69</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="H7" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
+      <c r="N7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
@@ -5004,19 +5048,27 @@
         <f t="shared" si="0"/>
         <v>17.8</v>
       </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="1"/>
+      <c r="F8" s="12">
+        <v>36</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="H8" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I8" s="12"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
+      <c r="N8" s="1">
+        <v>300</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
@@ -5092,7 +5144,7 @@
         <v>17.8</v>
       </c>
       <c r="F11" s="12"/>
-      <c r="G11" s="11"/>
+      <c r="G11" s="32"/>
       <c r="H11" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -5190,11 +5242,16 @@
         <f t="shared" si="0"/>
         <v>17.8</v>
       </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="1"/>
+      <c r="F14" s="12">
+        <f>47+9+10</f>
+        <v>66</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="H14" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I14" s="14" t="s">
         <v>69</v>
@@ -5415,11 +5472,16 @@
         <f t="shared" si="0"/>
         <v>17.8</v>
       </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="1"/>
+      <c r="F21" s="12">
+        <f>400+30+3</f>
+        <v>433</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="H21" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -5502,11 +5564,15 @@
         <f t="shared" si="0"/>
         <v>17.8</v>
       </c>
-      <c r="F24" s="12"/>
-      <c r="G24" s="1"/>
+      <c r="F24" s="12">
+        <v>58</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="H24" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I24" s="28" t="s">
         <v>86</v>
@@ -5799,7 +5865,7 @@
       <c r="G34" s="1"/>
       <c r="H34" s="6">
         <f>SUM(H2:H32)</f>
-        <v>35.6</v>
+        <v>697.6</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
